--- a/docs/ACC.xlsx
+++ b/docs/ACC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f261d42a834e88db/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Masters\Thesis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{C18979E8-6414-4F97-A76A-2A0F46140D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F525D2AF-80EB-45A2-AC51-EE302BD84B58}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1C888A-362F-4F3A-973D-AE2B82726F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0525AC44-D0D6-4FE0-AF0E-B743C2561208}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="16">
   <si>
     <t>*</t>
   </si>
@@ -70,6 +70,21 @@
   </si>
   <si>
     <t>R</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>32 rows</t>
+  </si>
+  <si>
+    <t>(64 / 8) * 128  = 2048 rows</t>
+  </si>
+  <si>
+    <t>(128 / 8) * 5    = 80      rows</t>
+  </si>
+  <si>
+    <t>(64 / 8)             = 8        rows</t>
   </si>
 </sst>
 </file>
@@ -119,7 +134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -150,6 +165,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -332,15 +353,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -418,9 +440,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -431,10 +450,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="20% - Accent1" xfId="4" builtinId="30"/>
     <cellStyle name="20% - Accent5" xfId="5" builtinId="46"/>
+    <cellStyle name="40% - Accent2" xfId="6" builtinId="35"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
@@ -984,38 +1013,38 @@
       <c r="X8" s="1">
         <v>13</v>
       </c>
-      <c r="AC8" s="29" t="s">
+      <c r="AC8" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29" t="s">
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="29" t="s">
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="AH8" s="29"/>
-      <c r="AI8" s="29" t="s">
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="AJ8" s="29"/>
-      <c r="AK8" s="29" t="s">
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="AL8" s="29"/>
-      <c r="AM8" s="29" t="s">
+      <c r="AL8" s="33"/>
+      <c r="AM8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29" t="s">
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="AP8" s="29"/>
-      <c r="AQ8" s="29" t="s">
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AR8" s="29"/>
+      <c r="AR8" s="33"/>
     </row>
     <row r="9" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D9" s="1"/>
@@ -1693,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9732E8-CFFA-4037-A877-E2234A02554C}">
-  <dimension ref="D5:AR78"/>
+  <dimension ref="C5:AR131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="13" width="3.85546875" customWidth="1"/>
@@ -1923,38 +1952,38 @@
       <c r="AB8" t="s">
         <v>9</v>
       </c>
-      <c r="AC8" s="29" t="s">
+      <c r="AC8" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29" t="s">
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="29" t="s">
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="AH8" s="29"/>
-      <c r="AI8" s="29" t="s">
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="AJ8" s="29"/>
-      <c r="AK8" s="29" t="s">
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="AL8" s="29"/>
-      <c r="AM8" s="29" t="s">
+      <c r="AL8" s="33"/>
+      <c r="AM8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29" t="s">
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="AP8" s="29"/>
-      <c r="AQ8" s="29" t="s">
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AR8" s="29"/>
+      <c r="AR8" s="33"/>
     </row>
     <row r="9" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D9" s="1"/>
@@ -2644,7 +2673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O17" s="15">
         <v>9</v>
       </c>
@@ -2724,7 +2753,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O18" s="15">
         <v>10</v>
       </c>
@@ -2804,7 +2833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:44" x14ac:dyDescent="0.25">
       <c r="AB19">
         <v>11</v>
       </c>
@@ -2813,7 +2842,7 @@
       <c r="AE19" s="13"/>
       <c r="AF19" s="14"/>
     </row>
-    <row r="20" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:44" x14ac:dyDescent="0.25">
       <c r="AB20">
         <v>12</v>
       </c>
@@ -2822,7 +2851,7 @@
       <c r="AE20" s="13"/>
       <c r="AF20" s="14"/>
     </row>
-    <row r="21" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O21" s="4">
         <v>9</v>
       </c>
@@ -2837,7 +2866,7 @@
       <c r="AE21" s="13"/>
       <c r="AF21" s="14"/>
     </row>
-    <row r="22" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O22" s="7">
         <v>10</v>
       </c>
@@ -2852,7 +2881,7 @@
       <c r="AE22" s="13"/>
       <c r="AF22" s="14"/>
     </row>
-    <row r="23" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O23" s="7">
         <v>11</v>
       </c>
@@ -2867,7 +2896,7 @@
       <c r="AE23" s="13"/>
       <c r="AF23" s="14"/>
     </row>
-    <row r="24" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O24" s="7">
         <v>12</v>
       </c>
@@ -2882,7 +2911,7 @@
       <c r="AE24" s="13"/>
       <c r="AF24" s="14"/>
     </row>
-    <row r="25" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O25" s="7">
         <v>13</v>
       </c>
@@ -2897,7 +2926,7 @@
       <c r="AE25" s="13"/>
       <c r="AF25" s="14"/>
     </row>
-    <row r="26" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O26" s="7">
         <v>14</v>
       </c>
@@ -2912,7 +2941,7 @@
       <c r="AE26" s="13"/>
       <c r="AF26" s="14"/>
     </row>
-    <row r="27" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O27" s="7">
         <v>15</v>
       </c>
@@ -2927,7 +2956,7 @@
       <c r="AE27" s="15"/>
       <c r="AF27" s="18"/>
     </row>
-    <row r="28" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:44" x14ac:dyDescent="0.25">
       <c r="O28" s="19">
         <v>16</v>
       </c>
@@ -2942,7 +2971,21 @@
       <c r="AE28" s="15"/>
       <c r="AF28" s="18"/>
     </row>
-    <row r="31" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:44" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="5:44" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31">
+        <v>8</v>
+      </c>
       <c r="O31" s="22">
         <v>17</v>
       </c>
@@ -2950,13 +2993,37 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="15:44" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:44" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
       <c r="O32" s="16">
         <v>18</v>
       </c>
       <c r="P32" s="25">
         <v>19</v>
       </c>
+    </row>
+    <row r="33" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="AC33" s="35"/>
+      <c r="AD33" s="35"/>
+      <c r="AE33" s="35"/>
+      <c r="AF33" s="35"/>
+      <c r="AG33" s="35"/>
+      <c r="AH33" s="35"/>
+      <c r="AI33" s="35"/>
+      <c r="AJ33" s="35"/>
+      <c r="AK33" s="35"/>
+      <c r="AL33" s="35"/>
+      <c r="AM33" s="35"/>
+      <c r="AN33" s="35"/>
+      <c r="AO33" s="35"/>
+      <c r="AP33" s="35"/>
+      <c r="AQ33" s="35"/>
+      <c r="AR33" s="35"/>
     </row>
     <row r="36" spans="4:44" x14ac:dyDescent="0.25">
       <c r="I36" t="s">
@@ -2965,1116 +3032,1623 @@
     </row>
     <row r="37" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D37" s="14">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E37" s="14">
+        <v>25</v>
+      </c>
+      <c r="F37" s="14">
+        <v>49</v>
+      </c>
+      <c r="G37" s="14">
+        <v>73</v>
+      </c>
+      <c r="H37" s="14">
+        <v>97</v>
+      </c>
+      <c r="I37" s="32"/>
+      <c r="O37" s="29">
+        <v>1</v>
+      </c>
+      <c r="P37" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="14">
         <v>2</v>
       </c>
-      <c r="F37" s="14">
-        <v>1</v>
-      </c>
-      <c r="G37" s="14">
-        <v>1</v>
-      </c>
-      <c r="H37" s="14">
+      <c r="R37" s="14">
         <v>3</v>
       </c>
-      <c r="I37" s="33"/>
-      <c r="O37" s="30">
-        <v>1</v>
-      </c>
-      <c r="P37" s="14">
-        <v>11</v>
-      </c>
-      <c r="Q37" s="14">
-        <v>11</v>
-      </c>
-      <c r="R37" s="14">
-        <v>11</v>
-      </c>
       <c r="S37" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T37" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="U37" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="V37" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W37" s="14">
-        <v>11</v>
-      </c>
-      <c r="X37" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB37" t="s">
         <v>9</v>
       </c>
-      <c r="AC37" s="29" t="s">
+      <c r="AC37" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="AD37" s="29"/>
-      <c r="AE37" s="29" t="s">
+      <c r="AD37" s="33"/>
+      <c r="AE37" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="AF37" s="29"/>
-      <c r="AG37" s="29" t="s">
+      <c r="AF37" s="33"/>
+      <c r="AG37" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="AH37" s="29"/>
-      <c r="AI37" s="29" t="s">
+      <c r="AH37" s="33"/>
+      <c r="AI37" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="AJ37" s="29"/>
-      <c r="AK37" s="29" t="s">
+      <c r="AJ37" s="33"/>
+      <c r="AK37" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="AL37" s="29"/>
-      <c r="AM37" s="29" t="s">
+      <c r="AL37" s="33"/>
+      <c r="AM37" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="AN37" s="29"/>
-      <c r="AO37" s="29" t="s">
+      <c r="AN37" s="33"/>
+      <c r="AO37" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="AP37" s="29"/>
-      <c r="AQ37" s="29" t="s">
+      <c r="AP37" s="33"/>
+      <c r="AQ37" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AR37" s="29"/>
+      <c r="AR37" s="33"/>
     </row>
     <row r="38" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D38" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E38" s="14">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F38" s="14">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G38" s="14">
+        <v>74</v>
+      </c>
+      <c r="H38" s="14">
+        <v>98</v>
+      </c>
+      <c r="I38" s="32"/>
+      <c r="O38" s="30">
         <v>2</v>
       </c>
-      <c r="H38" s="14">
-        <v>6</v>
-      </c>
-      <c r="I38" s="33"/>
-      <c r="O38" s="31">
-        <v>2</v>
-      </c>
       <c r="P38" s="14">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Q38" s="14">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="R38" s="14">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="S38" s="14">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="T38" s="14">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="U38" s="14">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="V38" s="14">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="W38" s="14">
-        <v>12</v>
-      </c>
-      <c r="X38" s="14">
-        <v>12</v>
-      </c>
-      <c r="AC38" s="14">
-        <v>11</v>
-      </c>
-      <c r="AD38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AE38" s="14">
-        <v>11</v>
-      </c>
-      <c r="AF38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="14">
-        <v>11</v>
-      </c>
-      <c r="AH38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AI38" s="14">
-        <v>11</v>
-      </c>
-      <c r="AJ38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AK38" s="14">
-        <v>11</v>
-      </c>
-      <c r="AL38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AM38" s="14">
-        <v>11</v>
-      </c>
-      <c r="AN38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AO38" s="14">
-        <v>11</v>
-      </c>
-      <c r="AP38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AQ38" s="14">
-        <v>11</v>
-      </c>
-      <c r="AR38" s="13">
-        <v>1</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="13"/>
+      <c r="AE38" s="14"/>
+      <c r="AF38" s="13"/>
+      <c r="AG38" s="14"/>
+      <c r="AH38" s="13"/>
+      <c r="AI38" s="14"/>
+      <c r="AJ38" s="13"/>
+      <c r="AK38" s="14"/>
+      <c r="AL38" s="13"/>
+      <c r="AM38" s="14"/>
+      <c r="AN38" s="13"/>
+      <c r="AO38" s="14"/>
+      <c r="AP38" s="13"/>
+      <c r="AQ38" s="14"/>
+      <c r="AR38" s="13"/>
     </row>
     <row r="39" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D39" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E39" s="14">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F39" s="14">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G39" s="14">
+        <v>75</v>
+      </c>
+      <c r="H39" s="14">
+        <v>99</v>
+      </c>
+      <c r="I39" s="32"/>
+      <c r="O39" s="30">
         <v>3</v>
       </c>
-      <c r="H39" s="14">
-        <v>9</v>
-      </c>
-      <c r="I39" s="33"/>
-      <c r="O39" s="31">
-        <v>3</v>
-      </c>
       <c r="P39" s="14">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="Q39" s="14">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="R39" s="14">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="S39" s="14">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="T39" s="14">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="U39" s="14">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="V39" s="14">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="W39" s="14">
-        <v>13</v>
-      </c>
-      <c r="X39" s="14">
-        <v>13</v>
-      </c>
-      <c r="AC39" s="14">
-        <v>12</v>
-      </c>
-      <c r="AD39" s="13">
-        <v>2</v>
-      </c>
-      <c r="AE39" s="14">
-        <v>12</v>
-      </c>
-      <c r="AF39" s="13">
-        <v>2</v>
-      </c>
-      <c r="AG39" s="14">
-        <v>12</v>
-      </c>
-      <c r="AH39" s="13">
-        <v>2</v>
-      </c>
-      <c r="AI39" s="14">
-        <v>12</v>
-      </c>
-      <c r="AJ39" s="13">
-        <v>2</v>
-      </c>
-      <c r="AK39" s="14">
-        <v>12</v>
-      </c>
-      <c r="AL39" s="13">
-        <v>2</v>
-      </c>
-      <c r="AM39" s="14">
-        <v>12</v>
-      </c>
-      <c r="AN39" s="13">
-        <v>2</v>
-      </c>
-      <c r="AO39" s="14">
-        <v>12</v>
-      </c>
-      <c r="AP39" s="13">
-        <v>2</v>
-      </c>
-      <c r="AQ39" s="14">
-        <v>12</v>
-      </c>
-      <c r="AR39" s="13">
-        <v>2</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="14"/>
+      <c r="AF39" s="13"/>
+      <c r="AG39" s="14"/>
+      <c r="AH39" s="13"/>
+      <c r="AI39" s="14"/>
+      <c r="AJ39" s="13"/>
+      <c r="AK39" s="14"/>
+      <c r="AL39" s="13"/>
+      <c r="AM39" s="14"/>
+      <c r="AN39" s="13"/>
+      <c r="AO39" s="14"/>
+      <c r="AP39" s="13"/>
+      <c r="AQ39" s="14"/>
+      <c r="AR39" s="13"/>
     </row>
     <row r="40" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D40" s="14">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E40" s="14">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F40" s="14">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="G40" s="14">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="H40" s="14">
-        <v>12</v>
-      </c>
-      <c r="I40" s="33"/>
-      <c r="O40" s="31">
+        <v>100</v>
+      </c>
+      <c r="I40" s="32"/>
+      <c r="O40" s="30">
         <v>4</v>
       </c>
       <c r="P40" s="14">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="Q40" s="14">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="R40" s="14">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="S40" s="14">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="T40" s="14">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="U40" s="14">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="V40" s="14">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="W40" s="14">
-        <v>14</v>
-      </c>
-      <c r="X40" s="14">
-        <v>14</v>
-      </c>
-      <c r="AC40" s="14">
-        <v>13</v>
-      </c>
-      <c r="AD40" s="13">
-        <v>3</v>
-      </c>
-      <c r="AE40" s="14">
-        <v>13</v>
-      </c>
-      <c r="AF40" s="13">
-        <v>3</v>
-      </c>
-      <c r="AG40" s="14">
-        <v>13</v>
-      </c>
-      <c r="AH40" s="13">
-        <v>3</v>
-      </c>
-      <c r="AI40" s="14">
-        <v>13</v>
-      </c>
-      <c r="AJ40" s="13">
-        <v>3</v>
-      </c>
-      <c r="AK40" s="14">
-        <v>13</v>
-      </c>
-      <c r="AL40" s="13">
-        <v>3</v>
-      </c>
-      <c r="AM40" s="14">
-        <v>13</v>
-      </c>
-      <c r="AN40" s="13">
-        <v>3</v>
-      </c>
-      <c r="AO40" s="14">
-        <v>13</v>
-      </c>
-      <c r="AP40" s="13">
-        <v>3</v>
-      </c>
-      <c r="AQ40" s="14">
-        <v>13</v>
-      </c>
-      <c r="AR40" s="13">
-        <v>3</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="AC40" s="14"/>
+      <c r="AD40" s="13"/>
+      <c r="AE40" s="14"/>
+      <c r="AF40" s="13"/>
+      <c r="AG40" s="14"/>
+      <c r="AH40" s="13"/>
+      <c r="AI40" s="14"/>
+      <c r="AJ40" s="13"/>
+      <c r="AK40" s="14"/>
+      <c r="AL40" s="13"/>
+      <c r="AM40" s="14"/>
+      <c r="AN40" s="13"/>
+      <c r="AO40" s="14"/>
+      <c r="AP40" s="13"/>
+      <c r="AQ40" s="14"/>
+      <c r="AR40" s="13"/>
     </row>
     <row r="41" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D41" s="14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F41" s="14">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="G41" s="14">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="H41" s="14">
-        <v>15</v>
-      </c>
-      <c r="I41" s="33"/>
-      <c r="O41" s="32">
+        <v>101</v>
+      </c>
+      <c r="I41" s="32"/>
+      <c r="O41" s="31">
         <v>5</v>
       </c>
       <c r="P41" s="14">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="Q41" s="14">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="R41" s="14">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="S41" s="14">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="T41" s="14">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="U41" s="14">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="V41" s="14">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="W41" s="14">
-        <v>15</v>
-      </c>
-      <c r="X41" s="14">
-        <v>15</v>
-      </c>
-      <c r="AC41" s="14">
-        <v>14</v>
-      </c>
-      <c r="AD41" s="13">
-        <v>4</v>
-      </c>
-      <c r="AE41" s="14">
-        <v>14</v>
-      </c>
-      <c r="AF41" s="13">
-        <v>4</v>
-      </c>
-      <c r="AG41" s="14">
-        <v>14</v>
-      </c>
-      <c r="AH41" s="13">
-        <v>4</v>
-      </c>
-      <c r="AI41" s="14">
-        <v>14</v>
-      </c>
-      <c r="AJ41" s="13">
-        <v>4</v>
-      </c>
-      <c r="AK41" s="14">
-        <v>14</v>
-      </c>
-      <c r="AL41" s="13">
-        <v>4</v>
-      </c>
-      <c r="AM41" s="14">
-        <v>14</v>
-      </c>
-      <c r="AN41" s="13">
-        <v>4</v>
-      </c>
-      <c r="AO41" s="14">
-        <v>14</v>
-      </c>
-      <c r="AP41" s="13">
-        <v>4</v>
-      </c>
-      <c r="AQ41" s="14">
-        <v>14</v>
-      </c>
-      <c r="AR41" s="13">
-        <v>4</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="AC41" s="14"/>
+      <c r="AD41" s="13"/>
+      <c r="AE41" s="14"/>
+      <c r="AF41" s="13"/>
+      <c r="AG41" s="14"/>
+      <c r="AH41" s="13"/>
+      <c r="AI41" s="14"/>
+      <c r="AJ41" s="13"/>
+      <c r="AK41" s="14"/>
+      <c r="AL41" s="13"/>
+      <c r="AM41" s="14"/>
+      <c r="AN41" s="13"/>
+      <c r="AO41" s="14"/>
+      <c r="AP41" s="13"/>
+      <c r="AQ41" s="14"/>
+      <c r="AR41" s="13"/>
     </row>
     <row r="42" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D42" s="14">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E42" s="14">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F42" s="14">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="G42" s="14">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="H42" s="14">
-        <v>18</v>
-      </c>
-      <c r="I42" s="33"/>
-      <c r="AC42" s="14">
-        <v>15</v>
-      </c>
-      <c r="AD42" s="13">
+        <v>102</v>
+      </c>
+      <c r="I42" s="32"/>
+      <c r="P42" s="32">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="32">
+        <v>2</v>
+      </c>
+      <c r="R42" s="32">
+        <v>3</v>
+      </c>
+      <c r="S42" s="32">
+        <v>4</v>
+      </c>
+      <c r="T42" s="32">
         <v>5</v>
       </c>
-      <c r="AE42" s="14">
-        <v>15</v>
-      </c>
-      <c r="AF42" s="13">
-        <v>5</v>
-      </c>
-      <c r="AG42" s="14">
-        <v>15</v>
-      </c>
-      <c r="AH42" s="13">
-        <v>5</v>
-      </c>
-      <c r="AI42" s="14">
-        <v>15</v>
-      </c>
-      <c r="AJ42" s="13">
-        <v>5</v>
-      </c>
-      <c r="AK42" s="14">
-        <v>15</v>
-      </c>
-      <c r="AL42" s="13">
-        <v>5</v>
-      </c>
-      <c r="AM42" s="14">
-        <v>15</v>
-      </c>
-      <c r="AN42" s="13">
-        <v>5</v>
-      </c>
-      <c r="AO42" s="14">
-        <v>15</v>
-      </c>
-      <c r="AP42" s="13">
-        <v>5</v>
-      </c>
-      <c r="AQ42" s="14">
-        <v>15</v>
-      </c>
-      <c r="AR42" s="13">
-        <v>5</v>
-      </c>
+      <c r="U42" s="32">
+        <v>6</v>
+      </c>
+      <c r="V42" s="32">
+        <v>7</v>
+      </c>
+      <c r="W42" s="32">
+        <v>8</v>
+      </c>
+      <c r="AC42" s="14"/>
+      <c r="AD42" s="13"/>
+      <c r="AE42" s="14"/>
+      <c r="AF42" s="13"/>
+      <c r="AG42" s="14"/>
+      <c r="AH42" s="13"/>
+      <c r="AI42" s="14"/>
+      <c r="AJ42" s="13"/>
+      <c r="AK42" s="14"/>
+      <c r="AL42" s="13"/>
+      <c r="AM42" s="14"/>
+      <c r="AN42" s="13"/>
+      <c r="AO42" s="14"/>
+      <c r="AP42" s="13"/>
+      <c r="AQ42" s="14"/>
+      <c r="AR42" s="13"/>
     </row>
     <row r="43" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D43" s="14">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E43" s="14">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F43" s="14">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G43" s="14">
-        <v>10.6</v>
+        <v>79</v>
       </c>
       <c r="H43" s="14">
-        <v>21</v>
-      </c>
-      <c r="I43" s="33"/>
-      <c r="AC43" s="33"/>
-      <c r="AD43" s="33"/>
-      <c r="AE43" s="33"/>
-      <c r="AF43" s="33"/>
-      <c r="AG43" s="33"/>
-      <c r="AH43" s="33"/>
-      <c r="AI43" s="33"/>
-      <c r="AJ43" s="33"/>
-      <c r="AK43" s="33"/>
-      <c r="AL43" s="33"/>
-      <c r="AM43" s="33"/>
-      <c r="AN43" s="33"/>
-      <c r="AO43" s="33"/>
-      <c r="AP43" s="33"/>
-      <c r="AQ43" s="33"/>
-      <c r="AR43" s="33"/>
+        <v>103</v>
+      </c>
+      <c r="I43" s="32"/>
+      <c r="O43" s="29">
+        <v>1</v>
+      </c>
+      <c r="P43" s="14">
+        <v>121</v>
+      </c>
+      <c r="Q43" s="14">
+        <v>122</v>
+      </c>
+      <c r="R43" s="14">
+        <v>123</v>
+      </c>
+      <c r="S43" s="14">
+        <v>124</v>
+      </c>
+      <c r="T43" s="14">
+        <v>125</v>
+      </c>
+      <c r="U43" s="14">
+        <v>126</v>
+      </c>
+      <c r="V43" s="14">
+        <v>127</v>
+      </c>
+      <c r="W43" s="14">
+        <v>128</v>
+      </c>
+      <c r="AC43" s="34"/>
+      <c r="AD43" s="34"/>
+      <c r="AE43" s="34"/>
+      <c r="AF43" s="34"/>
+      <c r="AG43" s="34"/>
+      <c r="AH43" s="34"/>
+      <c r="AI43" s="34"/>
+      <c r="AJ43" s="34"/>
+      <c r="AK43" s="34"/>
+      <c r="AL43" s="34"/>
+      <c r="AM43" s="34"/>
+      <c r="AN43" s="34"/>
+      <c r="AO43" s="34"/>
+      <c r="AP43" s="34"/>
+      <c r="AQ43" s="34"/>
+      <c r="AR43" s="34"/>
     </row>
     <row r="44" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D44" s="14">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E44" s="14">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F44" s="14">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="G44" s="14">
-        <v>12.3</v>
+        <v>80</v>
       </c>
       <c r="H44" s="14">
-        <v>24</v>
-      </c>
-      <c r="I44" s="33"/>
+        <v>104</v>
+      </c>
+      <c r="I44" s="32"/>
+      <c r="O44" s="30">
+        <v>2</v>
+      </c>
+      <c r="P44" s="14">
+        <v>145</v>
+      </c>
+      <c r="Q44" s="14">
+        <v>146</v>
+      </c>
+      <c r="R44" s="14">
+        <v>147</v>
+      </c>
+      <c r="S44" s="14">
+        <v>148</v>
+      </c>
+      <c r="T44" s="14">
+        <v>149</v>
+      </c>
+      <c r="U44" s="14">
+        <v>150</v>
+      </c>
+      <c r="V44" s="14">
+        <v>151</v>
+      </c>
+      <c r="W44" s="14">
+        <v>152</v>
+      </c>
     </row>
     <row r="45" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D45" s="14">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E45" s="14">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F45" s="14">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G45" s="14">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="H45" s="14">
-        <v>27</v>
-      </c>
-      <c r="I45" s="33"/>
+        <v>105</v>
+      </c>
+      <c r="I45" s="32"/>
+      <c r="O45" s="30">
+        <v>3</v>
+      </c>
+      <c r="P45" s="14">
+        <v>169</v>
+      </c>
+      <c r="Q45" s="14">
+        <v>170</v>
+      </c>
+      <c r="R45" s="14">
+        <v>171</v>
+      </c>
+      <c r="S45" s="14">
+        <v>172</v>
+      </c>
+      <c r="T45" s="14">
+        <v>173</v>
+      </c>
+      <c r="U45" s="14">
+        <v>174</v>
+      </c>
+      <c r="V45" s="14">
+        <v>175</v>
+      </c>
+      <c r="W45" s="14">
+        <v>176</v>
+      </c>
+      <c r="AC45" s="35"/>
+      <c r="AD45" s="35"/>
+      <c r="AE45" s="35"/>
+      <c r="AF45" s="35"/>
+      <c r="AG45" s="35"/>
+      <c r="AH45" s="35"/>
+      <c r="AI45" s="35"/>
+      <c r="AJ45" s="35"/>
+      <c r="AK45" s="35"/>
+      <c r="AL45" s="35"/>
+      <c r="AM45" s="35"/>
+      <c r="AN45" s="35"/>
+      <c r="AO45" s="35"/>
+      <c r="AP45" s="35"/>
+      <c r="AQ45" s="35"/>
+      <c r="AR45" s="35"/>
     </row>
     <row r="46" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D46" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E46" s="14">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F46" s="14">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="G46" s="14">
-        <v>15.7</v>
+        <v>82</v>
       </c>
       <c r="H46" s="14">
-        <v>30</v>
-      </c>
-      <c r="I46" s="33"/>
+        <v>106</v>
+      </c>
+      <c r="I46" s="32"/>
+      <c r="O46" s="30">
+        <v>4</v>
+      </c>
+      <c r="P46" s="14">
+        <v>193</v>
+      </c>
+      <c r="Q46" s="14">
+        <v>194</v>
+      </c>
+      <c r="R46" s="14">
+        <v>195</v>
+      </c>
+      <c r="S46" s="14">
+        <v>196</v>
+      </c>
+      <c r="T46" s="14">
+        <v>197</v>
+      </c>
+      <c r="U46" s="14">
+        <v>198</v>
+      </c>
+      <c r="V46" s="14">
+        <v>199</v>
+      </c>
+      <c r="W46" s="14">
+        <v>200</v>
+      </c>
+      <c r="AC46" s="35"/>
+      <c r="AD46" s="35"/>
+      <c r="AE46" s="35"/>
+      <c r="AF46" s="35"/>
+      <c r="AG46" s="35"/>
+      <c r="AH46" s="35"/>
+      <c r="AI46" s="35"/>
+      <c r="AJ46" s="35"/>
+      <c r="AK46" s="35"/>
+      <c r="AL46" s="35"/>
+      <c r="AM46" s="35"/>
+      <c r="AN46" s="35"/>
+      <c r="AO46" s="35"/>
+      <c r="AP46" s="35"/>
+      <c r="AQ46" s="35"/>
+      <c r="AR46" s="35"/>
     </row>
     <row r="47" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D47" s="14">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E47" s="14">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F47" s="14">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G47" s="14">
-        <v>17.399999999999999</v>
+        <v>83</v>
       </c>
       <c r="H47" s="14">
-        <v>33</v>
-      </c>
-      <c r="I47" s="33"/>
+        <v>107</v>
+      </c>
+      <c r="I47" s="32"/>
+      <c r="O47" s="31">
+        <v>5</v>
+      </c>
+      <c r="P47" s="14">
+        <v>217</v>
+      </c>
+      <c r="Q47" s="14">
+        <v>218</v>
+      </c>
+      <c r="R47" s="14">
+        <v>219</v>
+      </c>
+      <c r="S47" s="14">
+        <v>220</v>
+      </c>
+      <c r="T47" s="14">
+        <v>221</v>
+      </c>
+      <c r="U47" s="14">
+        <v>222</v>
+      </c>
+      <c r="V47" s="14">
+        <v>223</v>
+      </c>
+      <c r="W47" s="14">
+        <v>224</v>
+      </c>
+      <c r="AC47" s="35"/>
+      <c r="AD47" s="35"/>
+      <c r="AE47" s="35"/>
+      <c r="AF47" s="35"/>
+      <c r="AG47" s="35"/>
+      <c r="AH47" s="35"/>
+      <c r="AI47" s="35"/>
+      <c r="AJ47" s="35"/>
+      <c r="AK47" s="35"/>
+      <c r="AL47" s="35"/>
+      <c r="AM47" s="35"/>
+      <c r="AN47" s="35"/>
+      <c r="AO47" s="35"/>
+      <c r="AP47" s="35"/>
+      <c r="AQ47" s="35"/>
+      <c r="AR47" s="35"/>
     </row>
     <row r="48" spans="4:44" x14ac:dyDescent="0.25">
       <c r="D48" s="14">
+        <v>12</v>
+      </c>
+      <c r="E48" s="14">
+        <v>36</v>
+      </c>
+      <c r="F48" s="14">
+        <v>60</v>
+      </c>
+      <c r="G48" s="14">
+        <v>84</v>
+      </c>
+      <c r="H48" s="14">
+        <v>108</v>
+      </c>
+      <c r="I48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="32"/>
+      <c r="AC48" s="35"/>
+      <c r="AD48" s="35"/>
+      <c r="AE48" s="35"/>
+      <c r="AF48" s="35"/>
+      <c r="AG48" s="35"/>
+      <c r="AH48" s="35"/>
+      <c r="AI48" s="35"/>
+      <c r="AJ48" s="35"/>
+      <c r="AK48" s="35"/>
+      <c r="AL48" s="35"/>
+      <c r="AM48" s="35"/>
+      <c r="AN48" s="35"/>
+      <c r="AO48" s="35"/>
+      <c r="AP48" s="35"/>
+      <c r="AQ48" s="35"/>
+      <c r="AR48" s="35"/>
+    </row>
+    <row r="49" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D49" s="14">
+        <v>13</v>
+      </c>
+      <c r="E49" s="14">
+        <v>37</v>
+      </c>
+      <c r="F49" s="14">
+        <v>61</v>
+      </c>
+      <c r="G49" s="14">
+        <v>85</v>
+      </c>
+      <c r="H49" s="14">
+        <v>109</v>
+      </c>
+      <c r="I49" s="32"/>
+      <c r="O49" s="29">
+        <v>1</v>
+      </c>
+      <c r="P49" s="14">
+        <v>241</v>
+      </c>
+      <c r="Q49" s="14">
+        <v>242</v>
+      </c>
+      <c r="R49" s="14">
+        <v>243</v>
+      </c>
+      <c r="S49" s="14">
+        <v>244</v>
+      </c>
+      <c r="T49" s="14">
+        <v>245</v>
+      </c>
+      <c r="U49" s="14">
+        <v>246</v>
+      </c>
+      <c r="V49" s="14">
+        <v>247</v>
+      </c>
+      <c r="W49" s="14">
+        <v>248</v>
+      </c>
+      <c r="AC49" s="35"/>
+      <c r="AD49" s="35"/>
+      <c r="AE49" s="35"/>
+      <c r="AF49" s="35"/>
+      <c r="AG49" s="35"/>
+      <c r="AH49" s="35"/>
+      <c r="AI49" s="35"/>
+      <c r="AJ49" s="35"/>
+      <c r="AK49" s="35"/>
+      <c r="AL49" s="35"/>
+      <c r="AM49" s="35"/>
+      <c r="AN49" s="35"/>
+      <c r="AO49" s="35"/>
+      <c r="AP49" s="35"/>
+      <c r="AQ49" s="35"/>
+      <c r="AR49" s="35"/>
+    </row>
+    <row r="50" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D50" s="14">
+        <v>14</v>
+      </c>
+      <c r="E50" s="14">
+        <v>38</v>
+      </c>
+      <c r="F50" s="14">
+        <v>62</v>
+      </c>
+      <c r="G50" s="14">
+        <v>86</v>
+      </c>
+      <c r="H50" s="14">
+        <v>110</v>
+      </c>
+      <c r="I50" s="32"/>
+      <c r="O50" s="30">
+        <v>2</v>
+      </c>
+      <c r="P50" s="14">
+        <v>265</v>
+      </c>
+      <c r="Q50" s="14">
+        <v>266</v>
+      </c>
+      <c r="R50" s="14">
+        <v>267</v>
+      </c>
+      <c r="S50" s="14">
+        <v>268</v>
+      </c>
+      <c r="T50" s="14">
+        <v>269</v>
+      </c>
+      <c r="U50" s="14">
+        <v>270</v>
+      </c>
+      <c r="V50" s="14">
+        <v>271</v>
+      </c>
+      <c r="W50" s="14">
+        <v>272</v>
+      </c>
+      <c r="AC50" s="35"/>
+      <c r="AD50" s="35"/>
+      <c r="AE50" s="35"/>
+      <c r="AF50" s="35"/>
+      <c r="AG50" s="35"/>
+      <c r="AH50" s="35"/>
+      <c r="AI50" s="35"/>
+      <c r="AJ50" s="35"/>
+      <c r="AK50" s="35"/>
+      <c r="AL50" s="35"/>
+      <c r="AM50" s="35"/>
+      <c r="AN50" s="35"/>
+      <c r="AO50" s="35"/>
+      <c r="AP50" s="35"/>
+      <c r="AQ50" s="35"/>
+      <c r="AR50" s="35"/>
+    </row>
+    <row r="51" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D51" s="14">
+        <v>15</v>
+      </c>
+      <c r="E51" s="14">
+        <v>39</v>
+      </c>
+      <c r="F51" s="14">
+        <v>63</v>
+      </c>
+      <c r="G51" s="14">
+        <v>87</v>
+      </c>
+      <c r="H51" s="14">
+        <v>111</v>
+      </c>
+      <c r="I51" s="32"/>
+      <c r="O51" s="30">
+        <v>3</v>
+      </c>
+      <c r="P51" s="14">
+        <v>289</v>
+      </c>
+      <c r="Q51" s="14">
+        <v>290</v>
+      </c>
+      <c r="R51" s="14">
+        <v>291</v>
+      </c>
+      <c r="S51" s="14">
+        <v>292</v>
+      </c>
+      <c r="T51" s="14">
+        <v>293</v>
+      </c>
+      <c r="U51" s="14">
+        <v>294</v>
+      </c>
+      <c r="V51" s="14">
+        <v>295</v>
+      </c>
+      <c r="W51" s="14">
+        <v>296</v>
+      </c>
+      <c r="AC51" s="35"/>
+      <c r="AD51" s="35"/>
+      <c r="AE51" s="35"/>
+      <c r="AF51" s="35"/>
+      <c r="AG51" s="35"/>
+      <c r="AH51" s="35"/>
+      <c r="AI51" s="35"/>
+      <c r="AJ51" s="35"/>
+      <c r="AK51" s="35"/>
+      <c r="AL51" s="35"/>
+      <c r="AM51" s="35"/>
+      <c r="AN51" s="35"/>
+      <c r="AO51" s="35"/>
+      <c r="AP51" s="35"/>
+      <c r="AQ51" s="35"/>
+      <c r="AR51" s="35"/>
+    </row>
+    <row r="52" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D52" s="14">
+        <v>16</v>
+      </c>
+      <c r="E52" s="14">
+        <v>40</v>
+      </c>
+      <c r="F52" s="14">
+        <v>64</v>
+      </c>
+      <c r="G52" s="14">
+        <v>88</v>
+      </c>
+      <c r="H52" s="14">
+        <v>112</v>
+      </c>
+      <c r="I52" s="32"/>
+      <c r="O52" s="30">
+        <v>4</v>
+      </c>
+      <c r="P52" s="14">
+        <v>313</v>
+      </c>
+      <c r="Q52" s="14">
+        <v>314</v>
+      </c>
+      <c r="R52" s="14">
+        <v>315</v>
+      </c>
+      <c r="S52" s="14">
+        <v>316</v>
+      </c>
+      <c r="T52" s="14">
+        <v>317</v>
+      </c>
+      <c r="U52" s="14">
+        <v>318</v>
+      </c>
+      <c r="V52" s="14">
+        <v>319</v>
+      </c>
+      <c r="W52" s="14">
+        <v>320</v>
+      </c>
+      <c r="AC52" s="35"/>
+      <c r="AD52" s="35"/>
+      <c r="AE52" s="35"/>
+      <c r="AF52" s="35"/>
+      <c r="AG52" s="35"/>
+      <c r="AH52" s="35"/>
+      <c r="AI52" s="35"/>
+      <c r="AJ52" s="35"/>
+      <c r="AK52" s="35"/>
+      <c r="AL52" s="35"/>
+      <c r="AM52" s="35"/>
+      <c r="AN52" s="35"/>
+      <c r="AO52" s="35"/>
+      <c r="AP52" s="35"/>
+      <c r="AQ52" s="35"/>
+      <c r="AR52" s="35"/>
+    </row>
+    <row r="53" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D53" s="14">
+        <v>17</v>
+      </c>
+      <c r="E53" s="14">
+        <v>41</v>
+      </c>
+      <c r="F53" s="14">
+        <v>65</v>
+      </c>
+      <c r="G53" s="14">
+        <v>89</v>
+      </c>
+      <c r="H53" s="14">
+        <v>113</v>
+      </c>
+      <c r="I53" s="32"/>
+      <c r="O53" s="31">
+        <v>5</v>
+      </c>
+      <c r="P53" s="14">
+        <v>337</v>
+      </c>
+      <c r="Q53" s="14">
+        <v>338</v>
+      </c>
+      <c r="R53" s="14">
+        <v>339</v>
+      </c>
+      <c r="S53" s="14">
+        <v>340</v>
+      </c>
+      <c r="T53" s="14">
+        <v>341</v>
+      </c>
+      <c r="U53" s="14">
+        <v>342</v>
+      </c>
+      <c r="V53" s="14">
+        <v>343</v>
+      </c>
+      <c r="W53" s="14">
+        <v>344</v>
+      </c>
+      <c r="AC53" s="35"/>
+      <c r="AD53" s="35"/>
+      <c r="AE53" s="35"/>
+      <c r="AF53" s="35"/>
+      <c r="AG53" s="35"/>
+      <c r="AH53" s="35"/>
+      <c r="AI53" s="35"/>
+      <c r="AJ53" s="35"/>
+      <c r="AK53" s="35"/>
+      <c r="AL53" s="35"/>
+      <c r="AM53" s="35"/>
+      <c r="AN53" s="35"/>
+      <c r="AO53" s="35"/>
+      <c r="AP53" s="35"/>
+      <c r="AQ53" s="35"/>
+      <c r="AR53" s="35"/>
+    </row>
+    <row r="54" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D54" s="14">
+        <v>18</v>
+      </c>
+      <c r="E54" s="14">
+        <v>42</v>
+      </c>
+      <c r="F54" s="14">
+        <v>66</v>
+      </c>
+      <c r="G54" s="14">
+        <v>90</v>
+      </c>
+      <c r="H54" s="14">
+        <v>114</v>
+      </c>
+      <c r="I54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="32"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="32"/>
+      <c r="V54" s="32"/>
+      <c r="W54" s="32"/>
+      <c r="AC54" s="35"/>
+      <c r="AD54" s="35"/>
+      <c r="AE54" s="35"/>
+      <c r="AF54" s="35"/>
+      <c r="AG54" s="35"/>
+      <c r="AH54" s="35"/>
+      <c r="AI54" s="35"/>
+      <c r="AJ54" s="35"/>
+      <c r="AK54" s="35"/>
+      <c r="AL54" s="35"/>
+      <c r="AM54" s="35"/>
+      <c r="AN54" s="35"/>
+      <c r="AO54" s="35"/>
+      <c r="AP54" s="35"/>
+      <c r="AQ54" s="35"/>
+      <c r="AR54" s="35"/>
+    </row>
+    <row r="55" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D55" s="14">
+        <v>19</v>
+      </c>
+      <c r="E55" s="14">
+        <v>43</v>
+      </c>
+      <c r="F55" s="14">
+        <v>67</v>
+      </c>
+      <c r="G55" s="14">
+        <v>91</v>
+      </c>
+      <c r="H55" s="14">
+        <v>115</v>
+      </c>
+      <c r="I55" s="32"/>
+      <c r="O55" s="29">
+        <v>1</v>
+      </c>
+      <c r="P55" s="14">
+        <v>361</v>
+      </c>
+      <c r="Q55" s="14">
+        <v>362</v>
+      </c>
+      <c r="R55" s="14">
+        <v>363</v>
+      </c>
+      <c r="S55" s="14">
+        <v>364</v>
+      </c>
+      <c r="T55" s="14">
+        <v>365</v>
+      </c>
+      <c r="U55" s="14">
+        <v>366</v>
+      </c>
+      <c r="V55" s="14">
+        <v>367</v>
+      </c>
+      <c r="W55" s="14">
+        <v>368</v>
+      </c>
+      <c r="AC55" s="35"/>
+      <c r="AD55" s="35"/>
+      <c r="AE55" s="35"/>
+      <c r="AF55" s="35"/>
+      <c r="AG55" s="35"/>
+      <c r="AH55" s="35"/>
+      <c r="AI55" s="35"/>
+      <c r="AJ55" s="35"/>
+      <c r="AK55" s="35"/>
+      <c r="AL55" s="35"/>
+      <c r="AM55" s="35"/>
+      <c r="AN55" s="35"/>
+      <c r="AO55" s="35"/>
+      <c r="AP55" s="35"/>
+      <c r="AQ55" s="35"/>
+      <c r="AR55" s="35"/>
+    </row>
+    <row r="56" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D56" s="14">
+        <v>20</v>
+      </c>
+      <c r="E56" s="14">
+        <v>44</v>
+      </c>
+      <c r="F56" s="14">
+        <v>68</v>
+      </c>
+      <c r="G56" s="14">
+        <v>92</v>
+      </c>
+      <c r="H56" s="14">
+        <v>116</v>
+      </c>
+      <c r="I56" s="32"/>
+      <c r="O56" s="30">
+        <v>2</v>
+      </c>
+      <c r="P56" s="14">
+        <v>385</v>
+      </c>
+      <c r="Q56" s="14">
+        <v>386</v>
+      </c>
+      <c r="R56" s="14">
+        <v>387</v>
+      </c>
+      <c r="S56" s="14">
+        <v>388</v>
+      </c>
+      <c r="T56" s="14">
+        <v>389</v>
+      </c>
+      <c r="U56" s="14">
+        <v>390</v>
+      </c>
+      <c r="V56" s="14">
+        <v>391</v>
+      </c>
+      <c r="W56" s="14">
+        <v>392</v>
+      </c>
+      <c r="AC56" s="35"/>
+      <c r="AD56" s="35"/>
+      <c r="AE56" s="35"/>
+      <c r="AF56" s="35"/>
+      <c r="AG56" s="35"/>
+      <c r="AH56" s="35"/>
+      <c r="AI56" s="35"/>
+      <c r="AJ56" s="35"/>
+      <c r="AK56" s="35"/>
+      <c r="AL56" s="35"/>
+      <c r="AM56" s="35"/>
+      <c r="AN56" s="35"/>
+      <c r="AO56" s="35"/>
+      <c r="AP56" s="35"/>
+      <c r="AQ56" s="35"/>
+      <c r="AR56" s="35"/>
+    </row>
+    <row r="57" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D57" s="14">
+        <v>21</v>
+      </c>
+      <c r="E57" s="14">
+        <v>45</v>
+      </c>
+      <c r="F57" s="14">
+        <v>69</v>
+      </c>
+      <c r="G57" s="14">
+        <v>93</v>
+      </c>
+      <c r="H57" s="14">
+        <v>117</v>
+      </c>
+      <c r="I57" s="32"/>
+      <c r="O57" s="30">
+        <v>3</v>
+      </c>
+      <c r="P57" s="14">
+        <v>409</v>
+      </c>
+      <c r="Q57" s="14">
+        <v>410</v>
+      </c>
+      <c r="R57" s="14">
+        <v>411</v>
+      </c>
+      <c r="S57" s="14">
+        <v>412</v>
+      </c>
+      <c r="T57" s="14">
+        <v>413</v>
+      </c>
+      <c r="U57" s="14">
+        <v>414</v>
+      </c>
+      <c r="V57" s="14">
+        <v>415</v>
+      </c>
+      <c r="W57" s="14">
+        <v>416</v>
+      </c>
+      <c r="AC57" s="35"/>
+      <c r="AD57" s="35"/>
+      <c r="AE57" s="35"/>
+      <c r="AF57" s="35"/>
+      <c r="AG57" s="35"/>
+      <c r="AH57" s="35"/>
+      <c r="AI57" s="35"/>
+      <c r="AJ57" s="35"/>
+      <c r="AK57" s="35"/>
+      <c r="AL57" s="35"/>
+      <c r="AM57" s="35"/>
+      <c r="AN57" s="35"/>
+      <c r="AO57" s="35"/>
+      <c r="AP57" s="35"/>
+      <c r="AQ57" s="35"/>
+      <c r="AR57" s="35"/>
+    </row>
+    <row r="58" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D58" s="14">
         <v>22</v>
       </c>
-      <c r="E48" s="14">
+      <c r="E58" s="14">
+        <v>46</v>
+      </c>
+      <c r="F58" s="14">
+        <v>70</v>
+      </c>
+      <c r="G58" s="14">
+        <v>94</v>
+      </c>
+      <c r="H58" s="14">
+        <v>118</v>
+      </c>
+      <c r="I58" s="32"/>
+      <c r="O58" s="30">
+        <v>4</v>
+      </c>
+      <c r="P58" s="14">
+        <v>433</v>
+      </c>
+      <c r="Q58" s="14">
+        <v>434</v>
+      </c>
+      <c r="R58" s="14">
+        <v>435</v>
+      </c>
+      <c r="S58" s="14">
+        <v>436</v>
+      </c>
+      <c r="T58" s="14">
+        <v>437</v>
+      </c>
+      <c r="U58" s="14">
+        <v>438</v>
+      </c>
+      <c r="V58" s="14">
+        <v>439</v>
+      </c>
+      <c r="W58" s="14">
+        <v>440</v>
+      </c>
+      <c r="AC58" s="35"/>
+      <c r="AD58" s="35"/>
+      <c r="AE58" s="35"/>
+      <c r="AF58" s="35"/>
+      <c r="AG58" s="35"/>
+      <c r="AH58" s="35"/>
+      <c r="AI58" s="35"/>
+      <c r="AJ58" s="35"/>
+      <c r="AK58" s="35"/>
+      <c r="AL58" s="35"/>
+      <c r="AM58" s="35"/>
+      <c r="AN58" s="35"/>
+      <c r="AO58" s="35"/>
+      <c r="AP58" s="35"/>
+      <c r="AQ58" s="35"/>
+      <c r="AR58" s="35"/>
+    </row>
+    <row r="59" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D59" s="14">
+        <v>23</v>
+      </c>
+      <c r="E59" s="14">
+        <v>47</v>
+      </c>
+      <c r="F59" s="14">
+        <v>71</v>
+      </c>
+      <c r="G59" s="14">
+        <v>95</v>
+      </c>
+      <c r="H59" s="14">
+        <v>119</v>
+      </c>
+      <c r="I59" s="32"/>
+      <c r="O59" s="31">
+        <v>5</v>
+      </c>
+      <c r="P59" s="14">
+        <v>457</v>
+      </c>
+      <c r="Q59" s="14">
+        <v>458</v>
+      </c>
+      <c r="R59" s="14">
+        <v>459</v>
+      </c>
+      <c r="S59" s="14">
+        <v>460</v>
+      </c>
+      <c r="T59" s="14">
+        <v>461</v>
+      </c>
+      <c r="U59" s="14">
+        <v>462</v>
+      </c>
+      <c r="V59" s="14">
+        <v>463</v>
+      </c>
+      <c r="W59" s="14">
+        <v>464</v>
+      </c>
+      <c r="AC59" s="35"/>
+      <c r="AD59" s="35"/>
+      <c r="AE59" s="35"/>
+      <c r="AF59" s="35"/>
+      <c r="AG59" s="35"/>
+      <c r="AH59" s="35"/>
+      <c r="AI59" s="35"/>
+      <c r="AJ59" s="35"/>
+      <c r="AK59" s="35"/>
+      <c r="AL59" s="35"/>
+      <c r="AM59" s="35"/>
+      <c r="AN59" s="35"/>
+      <c r="AO59" s="35"/>
+      <c r="AP59" s="35"/>
+      <c r="AQ59" s="35"/>
+      <c r="AR59" s="35"/>
+    </row>
+    <row r="60" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D60" s="14">
         <v>24</v>
-      </c>
-      <c r="F48" s="14">
-        <v>23</v>
-      </c>
-      <c r="G48" s="14">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="H48" s="14">
-        <v>36</v>
-      </c>
-      <c r="I48" s="33"/>
-    </row>
-    <row r="49" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D49" s="14">
-        <v>23</v>
-      </c>
-      <c r="E49" s="14">
-        <v>26</v>
-      </c>
-      <c r="F49" s="14">
-        <v>25</v>
-      </c>
-      <c r="G49" s="14">
-        <v>20.8</v>
-      </c>
-      <c r="H49" s="14">
-        <v>39</v>
-      </c>
-      <c r="I49" s="33"/>
-    </row>
-    <row r="50" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D50" s="14">
-        <v>24</v>
-      </c>
-      <c r="E50" s="14">
-        <v>28</v>
-      </c>
-      <c r="F50" s="14">
-        <v>27</v>
-      </c>
-      <c r="G50" s="14">
-        <v>22.5</v>
-      </c>
-      <c r="H50" s="14">
-        <v>42</v>
-      </c>
-      <c r="I50" s="33"/>
-    </row>
-    <row r="51" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D51" s="14">
-        <v>25</v>
-      </c>
-      <c r="E51" s="14">
-        <v>30</v>
-      </c>
-      <c r="F51" s="14">
-        <v>29</v>
-      </c>
-      <c r="G51" s="14">
-        <v>24.2</v>
-      </c>
-      <c r="H51" s="14">
-        <v>45</v>
-      </c>
-      <c r="I51" s="33"/>
-    </row>
-    <row r="52" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D52" s="14">
-        <v>26</v>
-      </c>
-      <c r="E52" s="14">
-        <v>32</v>
-      </c>
-      <c r="F52" s="14">
-        <v>31</v>
-      </c>
-      <c r="G52" s="14">
-        <v>25.9</v>
-      </c>
-      <c r="H52" s="14">
-        <v>48</v>
-      </c>
-      <c r="I52" s="33"/>
-    </row>
-    <row r="53" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D53" s="14">
-        <v>27</v>
-      </c>
-      <c r="E53" s="14">
-        <v>34</v>
-      </c>
-      <c r="F53" s="14">
-        <v>33</v>
-      </c>
-      <c r="G53" s="14">
-        <v>27.6</v>
-      </c>
-      <c r="H53" s="14">
-        <v>51</v>
-      </c>
-      <c r="I53" s="33"/>
-    </row>
-    <row r="54" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D54" s="14">
-        <v>28</v>
-      </c>
-      <c r="E54" s="14">
-        <v>36</v>
-      </c>
-      <c r="F54" s="14">
-        <v>35</v>
-      </c>
-      <c r="G54" s="14">
-        <v>29.3</v>
-      </c>
-      <c r="H54" s="14">
-        <v>54</v>
-      </c>
-      <c r="I54" s="33"/>
-    </row>
-    <row r="55" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D55" s="14">
-        <v>29</v>
-      </c>
-      <c r="E55" s="14">
-        <v>38</v>
-      </c>
-      <c r="F55" s="14">
-        <v>37</v>
-      </c>
-      <c r="G55" s="14">
-        <v>31</v>
-      </c>
-      <c r="H55" s="14">
-        <v>57</v>
-      </c>
-      <c r="I55" s="33"/>
-    </row>
-    <row r="56" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D56" s="14">
-        <v>30</v>
-      </c>
-      <c r="E56" s="14">
-        <v>40</v>
-      </c>
-      <c r="F56" s="14">
-        <v>39</v>
-      </c>
-      <c r="G56" s="14">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="H56" s="14">
-        <v>60</v>
-      </c>
-      <c r="I56" s="33"/>
-    </row>
-    <row r="57" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D57" s="14">
-        <v>31</v>
-      </c>
-      <c r="E57" s="14">
-        <v>42</v>
-      </c>
-      <c r="F57" s="14">
-        <v>41</v>
-      </c>
-      <c r="G57" s="14">
-        <v>34.4</v>
-      </c>
-      <c r="H57" s="14">
-        <v>63</v>
-      </c>
-      <c r="I57" s="33"/>
-    </row>
-    <row r="58" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D58" s="14">
-        <v>32</v>
-      </c>
-      <c r="E58" s="14">
-        <v>44</v>
-      </c>
-      <c r="F58" s="14">
-        <v>43</v>
-      </c>
-      <c r="G58" s="14">
-        <v>36.1</v>
-      </c>
-      <c r="H58" s="14">
-        <v>66</v>
-      </c>
-      <c r="I58" s="33"/>
-    </row>
-    <row r="59" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D59" s="14">
-        <v>33</v>
-      </c>
-      <c r="E59" s="14">
-        <v>46</v>
-      </c>
-      <c r="F59" s="14">
-        <v>45</v>
-      </c>
-      <c r="G59" s="14">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="H59" s="14">
-        <v>69</v>
-      </c>
-      <c r="I59" s="33"/>
-    </row>
-    <row r="60" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D60" s="14">
-        <v>34</v>
       </c>
       <c r="E60" s="14">
         <v>48</v>
       </c>
       <c r="F60" s="14">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G60" s="14">
-        <v>39.5</v>
+        <v>96</v>
       </c>
       <c r="H60" s="14">
-        <v>72</v>
-      </c>
-      <c r="I60" s="33"/>
-    </row>
-    <row r="63" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D63" s="14">
+        <v>120</v>
+      </c>
+      <c r="I60" s="32"/>
+      <c r="P60" s="32"/>
+      <c r="Q60" s="32"/>
+      <c r="R60" s="32"/>
+      <c r="S60" s="32"/>
+      <c r="T60" s="32"/>
+      <c r="U60" s="32"/>
+      <c r="V60" s="32"/>
+      <c r="W60" s="32"/>
+      <c r="AC60" s="35"/>
+      <c r="AD60" s="35"/>
+      <c r="AE60" s="35"/>
+      <c r="AF60" s="35"/>
+      <c r="AG60" s="35"/>
+      <c r="AH60" s="35"/>
+      <c r="AI60" s="35"/>
+      <c r="AJ60" s="35"/>
+      <c r="AK60" s="35"/>
+      <c r="AL60" s="35"/>
+      <c r="AM60" s="35"/>
+      <c r="AN60" s="35"/>
+      <c r="AO60" s="35"/>
+      <c r="AP60" s="35"/>
+      <c r="AQ60" s="35"/>
+      <c r="AR60" s="35"/>
+    </row>
+    <row r="61" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D61" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" s="32"/>
+      <c r="O61" s="29">
         <v>1</v>
       </c>
-      <c r="E63" s="14">
+      <c r="P61" s="14">
+        <v>481</v>
+      </c>
+      <c r="Q61" s="14">
+        <v>482</v>
+      </c>
+      <c r="R61" s="14">
+        <v>483</v>
+      </c>
+      <c r="S61" s="14">
+        <v>484</v>
+      </c>
+      <c r="T61" s="14">
+        <v>485</v>
+      </c>
+      <c r="U61" s="14">
+        <v>486</v>
+      </c>
+      <c r="V61" s="14">
+        <v>487</v>
+      </c>
+      <c r="W61" s="14">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="62" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D62" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" s="32"/>
+      <c r="O62" s="30">
         <v>2</v>
       </c>
-      <c r="F63" s="14">
+      <c r="P62" s="14">
+        <v>505</v>
+      </c>
+      <c r="Q62" s="14">
+        <v>506</v>
+      </c>
+      <c r="R62" s="14">
+        <v>507</v>
+      </c>
+      <c r="S62" s="14">
+        <v>508</v>
+      </c>
+      <c r="T62" s="14">
+        <v>509</v>
+      </c>
+      <c r="U62" s="14">
+        <v>510</v>
+      </c>
+      <c r="V62" s="14">
+        <v>511</v>
+      </c>
+      <c r="W62" s="14">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="63" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D63" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" s="32"/>
+      <c r="O63" s="30">
         <v>3</v>
       </c>
-      <c r="G63" s="14">
+      <c r="P63" s="14">
+        <v>529</v>
+      </c>
+      <c r="Q63" s="14">
+        <v>530</v>
+      </c>
+      <c r="R63" s="14">
+        <v>531</v>
+      </c>
+      <c r="S63" s="14">
+        <v>532</v>
+      </c>
+      <c r="T63" s="14">
+        <v>533</v>
+      </c>
+      <c r="U63" s="14">
+        <v>534</v>
+      </c>
+      <c r="V63" s="14">
+        <v>535</v>
+      </c>
+      <c r="W63" s="14">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="64" spans="4:44" x14ac:dyDescent="0.25">
+      <c r="D64" s="14">
+        <v>128</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" s="32"/>
+      <c r="O64" s="30">
         <v>4</v>
       </c>
-      <c r="H63" s="14">
+      <c r="P64" s="14">
+        <v>553</v>
+      </c>
+      <c r="Q64" s="14">
+        <v>554</v>
+      </c>
+      <c r="R64" s="14">
+        <v>555</v>
+      </c>
+      <c r="S64" s="14">
+        <v>556</v>
+      </c>
+      <c r="T64" s="14">
+        <v>557</v>
+      </c>
+      <c r="U64" s="14">
+        <v>558</v>
+      </c>
+      <c r="V64" s="14">
+        <v>559</v>
+      </c>
+      <c r="W64" s="14">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="65" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="O65" s="31">
         <v>5</v>
       </c>
-      <c r="I63" s="14">
-        <v>6</v>
-      </c>
-      <c r="J63" s="14">
-        <v>7</v>
-      </c>
-      <c r="K63" s="14">
-        <v>8</v>
-      </c>
-      <c r="L63" s="14">
-        <v>9</v>
-      </c>
-      <c r="M63" s="14">
-        <v>10</v>
-      </c>
-      <c r="N63" s="14">
-        <v>11</v>
-      </c>
-      <c r="O63" s="14">
-        <v>12</v>
-      </c>
-      <c r="P63" s="14">
-        <v>13</v>
-      </c>
-      <c r="Q63" s="14">
-        <v>14</v>
-      </c>
-      <c r="R63" s="14">
-        <v>15</v>
-      </c>
-      <c r="S63" s="14">
-        <v>16</v>
-      </c>
-      <c r="X63" s="13">
+      <c r="P65" s="14">
+        <v>577</v>
+      </c>
+      <c r="Q65" s="14">
+        <v>578</v>
+      </c>
+      <c r="R65" s="14">
+        <v>579</v>
+      </c>
+      <c r="S65" s="14">
+        <v>580</v>
+      </c>
+      <c r="T65" s="14">
+        <v>581</v>
+      </c>
+      <c r="U65" s="14">
+        <v>582</v>
+      </c>
+      <c r="V65" s="14">
+        <v>583</v>
+      </c>
+      <c r="W65" s="14">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="67" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D67" s="14">
         <v>1</v>
-      </c>
-      <c r="AC63" s="14">
-        <v>1</v>
-      </c>
-      <c r="AD63" s="14">
-        <v>2</v>
-      </c>
-      <c r="AE63" s="14">
-        <v>3</v>
-      </c>
-      <c r="AF63" s="14">
-        <v>4</v>
-      </c>
-      <c r="AG63" s="14">
-        <v>5</v>
-      </c>
-      <c r="AH63" s="14">
-        <v>6</v>
-      </c>
-      <c r="AI63" s="14">
-        <v>7</v>
-      </c>
-      <c r="AJ63" s="14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="4:36" x14ac:dyDescent="0.25">
-      <c r="D64" s="14">
-        <v>2</v>
-      </c>
-      <c r="E64" s="14">
-        <v>2</v>
-      </c>
-      <c r="F64" s="14">
-        <v>3</v>
-      </c>
-      <c r="G64" s="14">
-        <v>4</v>
-      </c>
-      <c r="H64" s="14">
-        <v>5</v>
-      </c>
-      <c r="I64" s="14">
-        <v>6</v>
-      </c>
-      <c r="J64" s="14">
-        <v>7</v>
-      </c>
-      <c r="K64" s="14">
-        <v>8</v>
-      </c>
-      <c r="L64" s="14">
-        <v>9</v>
-      </c>
-      <c r="M64" s="14">
-        <v>10</v>
-      </c>
-      <c r="N64" s="14">
-        <v>11</v>
-      </c>
-      <c r="O64" s="14">
-        <v>12</v>
-      </c>
-      <c r="P64" s="14">
-        <v>13</v>
-      </c>
-      <c r="Q64" s="14">
-        <v>14</v>
-      </c>
-      <c r="R64" s="14">
-        <v>15</v>
-      </c>
-      <c r="S64" s="14">
-        <v>16</v>
-      </c>
-      <c r="X64" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D65" s="14">
-        <v>3</v>
-      </c>
-      <c r="E65" s="14">
-        <v>2</v>
-      </c>
-      <c r="F65" s="14">
-        <v>3</v>
-      </c>
-      <c r="G65" s="14">
-        <v>4</v>
-      </c>
-      <c r="H65" s="14">
-        <v>5</v>
-      </c>
-      <c r="I65" s="14">
-        <v>6</v>
-      </c>
-      <c r="J65" s="14">
-        <v>7</v>
-      </c>
-      <c r="K65" s="14">
-        <v>8</v>
-      </c>
-      <c r="L65" s="14">
-        <v>9</v>
-      </c>
-      <c r="M65" s="14">
-        <v>10</v>
-      </c>
-      <c r="N65" s="14">
-        <v>11</v>
-      </c>
-      <c r="O65" s="14">
-        <v>12</v>
-      </c>
-      <c r="P65" s="14">
-        <v>13</v>
-      </c>
-      <c r="Q65" s="14">
-        <v>14</v>
-      </c>
-      <c r="R65" s="14">
-        <v>15</v>
-      </c>
-      <c r="S65" s="14">
-        <v>16</v>
-      </c>
-      <c r="X65" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D66" s="14">
-        <v>4</v>
-      </c>
-      <c r="E66" s="14">
-        <v>2</v>
-      </c>
-      <c r="F66" s="14">
-        <v>3</v>
-      </c>
-      <c r="G66" s="14">
-        <v>4</v>
-      </c>
-      <c r="H66" s="14">
-        <v>5</v>
-      </c>
-      <c r="I66" s="14">
-        <v>6</v>
-      </c>
-      <c r="J66" s="14">
-        <v>7</v>
-      </c>
-      <c r="K66" s="14">
-        <v>8</v>
-      </c>
-      <c r="L66" s="14">
-        <v>9</v>
-      </c>
-      <c r="M66" s="14">
-        <v>10</v>
-      </c>
-      <c r="N66" s="14">
-        <v>11</v>
-      </c>
-      <c r="O66" s="14">
-        <v>12</v>
-      </c>
-      <c r="P66" s="14">
-        <v>13</v>
-      </c>
-      <c r="Q66" s="14">
-        <v>14</v>
-      </c>
-      <c r="R66" s="14">
-        <v>15</v>
-      </c>
-      <c r="S66" s="14">
-        <v>16</v>
-      </c>
-      <c r="X66" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D67" s="14">
-        <v>5</v>
       </c>
       <c r="E67" s="14">
         <v>2</v>
@@ -4097,235 +4671,2211 @@
       <c r="K67" s="14">
         <v>8</v>
       </c>
-      <c r="L67" s="14">
+      <c r="O67" s="29">
+        <v>1</v>
+      </c>
+      <c r="P67" s="14">
+        <v>601</v>
+      </c>
+      <c r="Q67" s="14">
+        <v>602</v>
+      </c>
+      <c r="R67" s="14">
+        <v>603</v>
+      </c>
+      <c r="S67" s="14">
+        <v>604</v>
+      </c>
+      <c r="T67" s="14">
+        <v>605</v>
+      </c>
+      <c r="U67" s="14">
+        <v>606</v>
+      </c>
+      <c r="V67" s="14">
+        <v>607</v>
+      </c>
+      <c r="W67" s="14">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="68" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D68" s="14">
+        <v>25</v>
+      </c>
+      <c r="E68" s="14">
+        <v>26</v>
+      </c>
+      <c r="F68" s="14">
+        <v>27</v>
+      </c>
+      <c r="G68" s="14">
+        <v>28</v>
+      </c>
+      <c r="H68" s="14">
+        <v>29</v>
+      </c>
+      <c r="I68" s="14">
+        <v>30</v>
+      </c>
+      <c r="J68" s="14">
+        <v>31</v>
+      </c>
+      <c r="K68" s="14">
+        <v>32</v>
+      </c>
+      <c r="O68" s="30">
+        <v>2</v>
+      </c>
+      <c r="P68" s="14">
+        <v>625</v>
+      </c>
+      <c r="Q68" s="14">
+        <v>626</v>
+      </c>
+      <c r="R68" s="14">
+        <v>627</v>
+      </c>
+      <c r="S68" s="14">
+        <v>628</v>
+      </c>
+      <c r="T68" s="14">
+        <v>629</v>
+      </c>
+      <c r="U68" s="14">
+        <v>630</v>
+      </c>
+      <c r="V68" s="14">
+        <v>631</v>
+      </c>
+      <c r="W68" s="14">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="69" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D69" s="14">
+        <v>49</v>
+      </c>
+      <c r="E69" s="14">
+        <v>50</v>
+      </c>
+      <c r="F69" s="14">
+        <v>51</v>
+      </c>
+      <c r="G69" s="14">
+        <v>52</v>
+      </c>
+      <c r="H69" s="14">
+        <v>53</v>
+      </c>
+      <c r="I69" s="14">
+        <v>54</v>
+      </c>
+      <c r="J69" s="14">
+        <v>55</v>
+      </c>
+      <c r="K69" s="14">
+        <v>56</v>
+      </c>
+      <c r="O69" s="30">
+        <v>3</v>
+      </c>
+      <c r="P69" s="14">
+        <v>649</v>
+      </c>
+      <c r="Q69" s="14">
+        <v>650</v>
+      </c>
+      <c r="R69" s="14">
+        <v>651</v>
+      </c>
+      <c r="S69" s="14">
+        <v>652</v>
+      </c>
+      <c r="T69" s="14">
+        <v>653</v>
+      </c>
+      <c r="U69" s="14">
+        <v>654</v>
+      </c>
+      <c r="V69" s="14">
+        <v>655</v>
+      </c>
+      <c r="W69" s="14">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="70" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D70" s="14">
+        <v>73</v>
+      </c>
+      <c r="E70" s="14">
+        <v>74</v>
+      </c>
+      <c r="F70" s="14">
+        <v>75</v>
+      </c>
+      <c r="G70" s="14">
+        <v>76</v>
+      </c>
+      <c r="H70" s="14">
+        <v>77</v>
+      </c>
+      <c r="I70" s="14">
+        <v>78</v>
+      </c>
+      <c r="J70" s="14">
+        <v>79</v>
+      </c>
+      <c r="K70" s="14">
+        <v>80</v>
+      </c>
+      <c r="O70" s="30">
+        <v>4</v>
+      </c>
+      <c r="P70" s="14">
+        <v>673</v>
+      </c>
+      <c r="Q70" s="14">
+        <v>674</v>
+      </c>
+      <c r="R70" s="14">
+        <v>675</v>
+      </c>
+      <c r="S70" s="14">
+        <v>676</v>
+      </c>
+      <c r="T70" s="14">
+        <v>677</v>
+      </c>
+      <c r="U70" s="14">
+        <v>678</v>
+      </c>
+      <c r="V70" s="14">
+        <v>679</v>
+      </c>
+      <c r="W70" s="14">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="71" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D71" s="14">
+        <v>97</v>
+      </c>
+      <c r="E71" s="14">
+        <v>98</v>
+      </c>
+      <c r="F71" s="14">
+        <v>99</v>
+      </c>
+      <c r="G71" s="14">
+        <v>100</v>
+      </c>
+      <c r="H71" s="14">
+        <v>101</v>
+      </c>
+      <c r="I71" s="14">
+        <v>102</v>
+      </c>
+      <c r="J71" s="14">
+        <v>103</v>
+      </c>
+      <c r="K71" s="14">
+        <v>104</v>
+      </c>
+      <c r="O71" s="31">
+        <v>5</v>
+      </c>
+      <c r="P71" s="14">
+        <v>697</v>
+      </c>
+      <c r="Q71" s="14">
+        <v>698</v>
+      </c>
+      <c r="R71" s="14">
+        <v>699</v>
+      </c>
+      <c r="S71" s="14">
+        <v>700</v>
+      </c>
+      <c r="T71" s="14">
+        <v>701</v>
+      </c>
+      <c r="U71" s="14">
+        <v>702</v>
+      </c>
+      <c r="V71" s="14">
+        <v>703</v>
+      </c>
+      <c r="W71" s="14">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="72" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D72" s="14">
         <v>9</v>
       </c>
-      <c r="M67" s="14">
+      <c r="E72" s="14">
         <v>10</v>
       </c>
-      <c r="N67" s="14">
-        <v>11</v>
-      </c>
-      <c r="O67" s="14">
+      <c r="F72" s="14">
+        <v>11</v>
+      </c>
+      <c r="G72" s="14">
         <v>12</v>
       </c>
-      <c r="P67" s="14">
+      <c r="H72" s="14">
         <v>13</v>
       </c>
-      <c r="Q67" s="14">
+      <c r="I72" s="14">
         <v>14</v>
       </c>
-      <c r="R67" s="14">
+      <c r="J72" s="14">
         <v>15</v>
       </c>
-      <c r="S67" s="14">
+      <c r="K72" s="14">
         <v>16</v>
       </c>
-      <c r="X67" s="13">
+    </row>
+    <row r="73" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D73" s="14">
+        <v>33</v>
+      </c>
+      <c r="E73" s="14">
+        <v>34</v>
+      </c>
+      <c r="F73" s="14">
+        <v>35</v>
+      </c>
+      <c r="G73" s="14">
+        <v>36</v>
+      </c>
+      <c r="H73" s="14">
+        <v>37</v>
+      </c>
+      <c r="I73" s="14">
+        <v>38</v>
+      </c>
+      <c r="J73" s="14">
+        <v>39</v>
+      </c>
+      <c r="K73" s="14">
+        <v>40</v>
+      </c>
+      <c r="O73" s="29">
+        <v>1</v>
+      </c>
+      <c r="P73" s="14">
+        <v>721</v>
+      </c>
+      <c r="Q73" s="14">
+        <v>722</v>
+      </c>
+      <c r="R73" s="14">
+        <v>723</v>
+      </c>
+      <c r="S73" s="14">
+        <v>724</v>
+      </c>
+      <c r="T73" s="14">
+        <v>725</v>
+      </c>
+      <c r="U73" s="14">
+        <v>726</v>
+      </c>
+      <c r="V73" s="14">
+        <v>727</v>
+      </c>
+      <c r="W73" s="14">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="74" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D74" s="14">
+        <v>57</v>
+      </c>
+      <c r="E74" s="14">
+        <v>58</v>
+      </c>
+      <c r="F74" s="14">
+        <v>59</v>
+      </c>
+      <c r="G74" s="14">
+        <v>60</v>
+      </c>
+      <c r="H74" s="14">
+        <v>61</v>
+      </c>
+      <c r="I74" s="14">
+        <v>62</v>
+      </c>
+      <c r="J74" s="14">
+        <v>63</v>
+      </c>
+      <c r="K74" s="14">
+        <v>64</v>
+      </c>
+      <c r="O74" s="30">
+        <v>2</v>
+      </c>
+      <c r="P74" s="14">
+        <v>745</v>
+      </c>
+      <c r="Q74" s="14">
+        <v>746</v>
+      </c>
+      <c r="R74" s="14">
+        <v>747</v>
+      </c>
+      <c r="S74" s="14">
+        <v>748</v>
+      </c>
+      <c r="T74" s="14">
+        <v>749</v>
+      </c>
+      <c r="U74" s="14">
+        <v>750</v>
+      </c>
+      <c r="V74" s="14">
+        <v>751</v>
+      </c>
+      <c r="W74" s="14">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="75" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D75" s="14">
+        <v>81</v>
+      </c>
+      <c r="E75" s="14">
+        <v>82</v>
+      </c>
+      <c r="F75" s="14">
+        <v>83</v>
+      </c>
+      <c r="G75" s="14">
+        <v>84</v>
+      </c>
+      <c r="H75" s="14">
+        <v>85</v>
+      </c>
+      <c r="I75" s="14">
+        <v>86</v>
+      </c>
+      <c r="J75" s="14">
+        <v>87</v>
+      </c>
+      <c r="K75" s="14">
+        <v>88</v>
+      </c>
+      <c r="O75" s="30">
+        <v>3</v>
+      </c>
+      <c r="P75" s="14">
+        <v>769</v>
+      </c>
+      <c r="Q75" s="14">
+        <v>770</v>
+      </c>
+      <c r="R75" s="14">
+        <v>771</v>
+      </c>
+      <c r="S75" s="14">
+        <v>772</v>
+      </c>
+      <c r="T75" s="14">
+        <v>773</v>
+      </c>
+      <c r="U75" s="14">
+        <v>774</v>
+      </c>
+      <c r="V75" s="14">
+        <v>775</v>
+      </c>
+      <c r="W75" s="14">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="76" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D76" s="14">
+        <v>105</v>
+      </c>
+      <c r="E76" s="14">
+        <v>106</v>
+      </c>
+      <c r="F76" s="14">
+        <v>107</v>
+      </c>
+      <c r="G76" s="14">
+        <v>108</v>
+      </c>
+      <c r="H76" s="14">
+        <v>109</v>
+      </c>
+      <c r="I76" s="14">
+        <v>110</v>
+      </c>
+      <c r="J76" s="14">
+        <v>111</v>
+      </c>
+      <c r="K76" s="14">
+        <v>112</v>
+      </c>
+      <c r="O76" s="30">
+        <v>4</v>
+      </c>
+      <c r="P76" s="14">
+        <v>793</v>
+      </c>
+      <c r="Q76" s="14">
+        <v>794</v>
+      </c>
+      <c r="R76" s="14">
+        <v>795</v>
+      </c>
+      <c r="S76" s="14">
+        <v>796</v>
+      </c>
+      <c r="T76" s="14">
+        <v>797</v>
+      </c>
+      <c r="U76" s="14">
+        <v>798</v>
+      </c>
+      <c r="V76" s="14">
+        <v>799</v>
+      </c>
+      <c r="W76" s="14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="77" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D77" s="14">
+        <v>17</v>
+      </c>
+      <c r="E77" s="14">
+        <v>18</v>
+      </c>
+      <c r="F77" s="14">
+        <v>19</v>
+      </c>
+      <c r="G77" s="14">
+        <v>20</v>
+      </c>
+      <c r="H77" s="14">
+        <v>21</v>
+      </c>
+      <c r="I77" s="14">
+        <v>22</v>
+      </c>
+      <c r="J77" s="14">
+        <v>23</v>
+      </c>
+      <c r="K77" s="14">
+        <v>24</v>
+      </c>
+      <c r="O77" s="31">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D68" s="14">
-        <v>6</v>
-      </c>
-      <c r="E68" s="14">
+      <c r="P77" s="14">
+        <v>817</v>
+      </c>
+      <c r="Q77" s="14">
+        <v>818</v>
+      </c>
+      <c r="R77" s="14">
+        <v>819</v>
+      </c>
+      <c r="S77" s="14">
+        <v>820</v>
+      </c>
+      <c r="T77" s="14">
+        <v>821</v>
+      </c>
+      <c r="U77" s="14">
+        <v>822</v>
+      </c>
+      <c r="V77" s="14">
+        <v>823</v>
+      </c>
+      <c r="W77" s="14">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="78" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D78" s="14">
+        <v>41</v>
+      </c>
+      <c r="E78" s="14">
+        <v>42</v>
+      </c>
+      <c r="F78" s="14">
+        <v>43</v>
+      </c>
+      <c r="G78" s="14">
+        <v>44</v>
+      </c>
+      <c r="H78" s="14">
+        <v>45</v>
+      </c>
+      <c r="I78" s="14">
+        <v>46</v>
+      </c>
+      <c r="J78" s="14">
+        <v>47</v>
+      </c>
+      <c r="K78" s="14">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D79" s="14">
+        <v>65</v>
+      </c>
+      <c r="E79" s="14">
+        <v>66</v>
+      </c>
+      <c r="F79" s="14">
+        <v>67</v>
+      </c>
+      <c r="G79" s="14">
+        <v>68</v>
+      </c>
+      <c r="H79" s="14">
+        <v>69</v>
+      </c>
+      <c r="I79" s="14">
+        <v>70</v>
+      </c>
+      <c r="J79" s="14">
+        <v>71</v>
+      </c>
+      <c r="K79" s="14">
+        <v>72</v>
+      </c>
+      <c r="O79" s="29">
+        <v>1</v>
+      </c>
+      <c r="P79" s="14">
+        <v>841</v>
+      </c>
+      <c r="Q79" s="14">
+        <v>842</v>
+      </c>
+      <c r="R79" s="14">
+        <v>843</v>
+      </c>
+      <c r="S79" s="14">
+        <v>844</v>
+      </c>
+      <c r="T79" s="14">
+        <v>845</v>
+      </c>
+      <c r="U79" s="14">
+        <v>846</v>
+      </c>
+      <c r="V79" s="14">
+        <v>847</v>
+      </c>
+      <c r="W79" s="14">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="80" spans="4:23" x14ac:dyDescent="0.25">
+      <c r="D80" s="14">
+        <v>89</v>
+      </c>
+      <c r="E80" s="14">
+        <v>90</v>
+      </c>
+      <c r="F80" s="14">
+        <v>91</v>
+      </c>
+      <c r="G80" s="14">
+        <v>92</v>
+      </c>
+      <c r="H80" s="14">
+        <v>93</v>
+      </c>
+      <c r="I80" s="14">
+        <v>94</v>
+      </c>
+      <c r="J80" s="14">
+        <v>95</v>
+      </c>
+      <c r="K80" s="14">
+        <v>96</v>
+      </c>
+      <c r="O80" s="30">
         <v>2</v>
       </c>
-      <c r="F68" s="14">
+      <c r="P80" s="14">
+        <v>865</v>
+      </c>
+      <c r="Q80" s="14">
+        <v>866</v>
+      </c>
+      <c r="R80" s="14">
+        <v>867</v>
+      </c>
+      <c r="S80" s="14">
+        <v>868</v>
+      </c>
+      <c r="T80" s="14">
+        <v>869</v>
+      </c>
+      <c r="U80" s="14">
+        <v>870</v>
+      </c>
+      <c r="V80" s="14">
+        <v>871</v>
+      </c>
+      <c r="W80" s="14">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="D81" s="14">
+        <v>113</v>
+      </c>
+      <c r="E81" s="14">
+        <v>114</v>
+      </c>
+      <c r="F81" s="14">
+        <v>115</v>
+      </c>
+      <c r="G81" s="14">
+        <v>116</v>
+      </c>
+      <c r="H81" s="14">
+        <v>117</v>
+      </c>
+      <c r="I81" s="14">
+        <v>118</v>
+      </c>
+      <c r="J81" s="14">
+        <v>119</v>
+      </c>
+      <c r="K81" s="14">
+        <v>120</v>
+      </c>
+      <c r="O81" s="30">
         <v>3</v>
       </c>
-      <c r="G68" s="14">
+      <c r="P81" s="14">
+        <v>889</v>
+      </c>
+      <c r="Q81" s="14">
+        <v>890</v>
+      </c>
+      <c r="R81" s="14">
+        <v>891</v>
+      </c>
+      <c r="S81" s="14">
+        <v>892</v>
+      </c>
+      <c r="T81" s="14">
+        <v>893</v>
+      </c>
+      <c r="U81" s="14">
+        <v>894</v>
+      </c>
+      <c r="V81" s="14">
+        <v>895</v>
+      </c>
+      <c r="W81" s="14">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="D82" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G82" s="14">
+        <v>128</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K82" s="14">
+        <v>129</v>
+      </c>
+      <c r="O82" s="30">
         <v>4</v>
       </c>
-      <c r="H68" s="14">
+      <c r="P82" s="14">
+        <v>913</v>
+      </c>
+      <c r="Q82" s="14">
+        <v>914</v>
+      </c>
+      <c r="R82" s="14">
+        <v>915</v>
+      </c>
+      <c r="S82" s="14">
+        <v>916</v>
+      </c>
+      <c r="T82" s="14">
+        <v>917</v>
+      </c>
+      <c r="U82" s="14">
+        <v>918</v>
+      </c>
+      <c r="V82" s="14">
+        <v>919</v>
+      </c>
+      <c r="W82" s="14">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="D83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="O83" s="31">
         <v>5</v>
       </c>
-      <c r="I68" s="14">
-        <v>6</v>
-      </c>
-      <c r="J68" s="14">
-        <v>7</v>
-      </c>
-      <c r="K68" s="14">
-        <v>8</v>
-      </c>
-      <c r="L68" s="14">
-        <v>9</v>
-      </c>
-      <c r="M68" s="14">
-        <v>10</v>
-      </c>
-      <c r="N68" s="14">
-        <v>11</v>
-      </c>
-      <c r="O68" s="14">
+      <c r="P83" s="14">
+        <v>937</v>
+      </c>
+      <c r="Q83" s="14">
+        <v>938</v>
+      </c>
+      <c r="R83" s="14">
+        <v>939</v>
+      </c>
+      <c r="S83" s="14">
+        <v>940</v>
+      </c>
+      <c r="T83" s="14">
+        <v>941</v>
+      </c>
+      <c r="U83" s="14">
+        <v>942</v>
+      </c>
+      <c r="V83" s="14">
+        <v>943</v>
+      </c>
+      <c r="W83" s="14">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="D84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="D85" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I85" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J85" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="O85" s="29">
+        <v>1</v>
+      </c>
+      <c r="P85" s="14">
+        <v>961</v>
+      </c>
+      <c r="Q85" s="14">
+        <v>962</v>
+      </c>
+      <c r="R85" s="14">
+        <v>963</v>
+      </c>
+      <c r="S85" s="14">
+        <v>964</v>
+      </c>
+      <c r="T85" s="14">
+        <v>965</v>
+      </c>
+      <c r="U85" s="14">
+        <v>966</v>
+      </c>
+      <c r="V85" s="14">
+        <v>967</v>
+      </c>
+      <c r="W85" s="14">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="C86" t="s">
         <v>12</v>
       </c>
-      <c r="P68" s="14">
-        <v>13</v>
-      </c>
-      <c r="Q68" s="14">
-        <v>14</v>
-      </c>
-      <c r="R68" s="14">
-        <v>15</v>
-      </c>
-      <c r="S68" s="14">
-        <v>16</v>
-      </c>
-      <c r="X68" s="13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D69" s="14">
-        <v>7</v>
-      </c>
-      <c r="E69" s="14">
+      <c r="D86" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I86" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="O86" s="30">
         <v>2</v>
       </c>
-      <c r="F69" s="14">
+      <c r="P86" s="14">
+        <v>985</v>
+      </c>
+      <c r="Q86" s="14">
+        <v>986</v>
+      </c>
+      <c r="R86" s="14">
+        <v>987</v>
+      </c>
+      <c r="S86" s="14">
+        <v>988</v>
+      </c>
+      <c r="T86" s="14">
+        <v>989</v>
+      </c>
+      <c r="U86" s="14">
+        <v>990</v>
+      </c>
+      <c r="V86" s="14">
+        <v>991</v>
+      </c>
+      <c r="W86" s="14">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="O87" s="30">
         <v>3</v>
       </c>
-      <c r="G69" s="14">
+      <c r="P87" s="14">
+        <v>1009</v>
+      </c>
+      <c r="Q87" s="14">
+        <v>1010</v>
+      </c>
+      <c r="R87" s="14">
+        <v>1011</v>
+      </c>
+      <c r="S87" s="14">
+        <v>1012</v>
+      </c>
+      <c r="T87" s="14">
+        <v>1013</v>
+      </c>
+      <c r="U87" s="14">
+        <v>1014</v>
+      </c>
+      <c r="V87" s="14">
+        <v>1015</v>
+      </c>
+      <c r="W87" s="14">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="O88" s="30">
         <v>4</v>
       </c>
-      <c r="H69" s="14">
+      <c r="P88" s="14">
+        <v>1033</v>
+      </c>
+      <c r="Q88" s="14">
+        <v>1034</v>
+      </c>
+      <c r="R88" s="14">
+        <v>1035</v>
+      </c>
+      <c r="S88" s="14">
+        <v>1036</v>
+      </c>
+      <c r="T88" s="14">
+        <v>1037</v>
+      </c>
+      <c r="U88" s="14">
+        <v>1038</v>
+      </c>
+      <c r="V88" s="14">
+        <v>1039</v>
+      </c>
+      <c r="W88" s="14">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="O89" s="31">
         <v>5</v>
       </c>
-      <c r="I69" s="14">
-        <v>6</v>
-      </c>
-      <c r="J69" s="14">
-        <v>7</v>
-      </c>
-      <c r="K69" s="14">
-        <v>8</v>
-      </c>
-      <c r="L69" s="14">
-        <v>9</v>
-      </c>
-      <c r="M69" s="14">
-        <v>10</v>
-      </c>
-      <c r="N69" s="14">
-        <v>11</v>
-      </c>
-      <c r="O69" s="14">
-        <v>12</v>
-      </c>
-      <c r="P69" s="14">
-        <v>13</v>
-      </c>
-      <c r="Q69" s="14">
-        <v>14</v>
-      </c>
-      <c r="R69" s="14">
-        <v>15</v>
-      </c>
-      <c r="S69" s="14">
-        <v>16</v>
-      </c>
-      <c r="X69" s="13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D70" s="14">
-        <v>8</v>
-      </c>
-      <c r="E70" s="14">
+      <c r="P89" s="14">
+        <v>1057</v>
+      </c>
+      <c r="Q89" s="14">
+        <v>1058</v>
+      </c>
+      <c r="R89" s="14">
+        <v>1059</v>
+      </c>
+      <c r="S89" s="14">
+        <v>1060</v>
+      </c>
+      <c r="T89" s="14">
+        <v>1061</v>
+      </c>
+      <c r="U89" s="14">
+        <v>1062</v>
+      </c>
+      <c r="V89" s="14">
+        <v>1063</v>
+      </c>
+      <c r="W89" s="14">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="O91" s="29">
+        <v>1</v>
+      </c>
+      <c r="P91" s="14">
+        <v>1081</v>
+      </c>
+      <c r="Q91" s="14">
+        <v>1082</v>
+      </c>
+      <c r="R91" s="14">
+        <v>1083</v>
+      </c>
+      <c r="S91" s="14">
+        <v>1084</v>
+      </c>
+      <c r="T91" s="14">
+        <v>1085</v>
+      </c>
+      <c r="U91" s="14">
+        <v>1086</v>
+      </c>
+      <c r="V91" s="14">
+        <v>1087</v>
+      </c>
+      <c r="W91" s="14">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="O92" s="30">
         <v>2</v>
       </c>
-      <c r="F70" s="14">
+      <c r="P92" s="14">
+        <v>1105</v>
+      </c>
+      <c r="Q92" s="14">
+        <v>1106</v>
+      </c>
+      <c r="R92" s="14">
+        <v>1107</v>
+      </c>
+      <c r="S92" s="14">
+        <v>1108</v>
+      </c>
+      <c r="T92" s="14">
+        <v>1109</v>
+      </c>
+      <c r="U92" s="14">
+        <v>1110</v>
+      </c>
+      <c r="V92" s="14">
+        <v>1111</v>
+      </c>
+      <c r="W92" s="14">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="O93" s="30">
         <v>3</v>
       </c>
-      <c r="G70" s="14">
+      <c r="P93" s="14">
+        <v>1129</v>
+      </c>
+      <c r="Q93" s="14">
+        <v>1130</v>
+      </c>
+      <c r="R93" s="14">
+        <v>1131</v>
+      </c>
+      <c r="S93" s="14">
+        <v>1132</v>
+      </c>
+      <c r="T93" s="14">
+        <v>1133</v>
+      </c>
+      <c r="U93" s="14">
+        <v>1134</v>
+      </c>
+      <c r="V93" s="14">
+        <v>1135</v>
+      </c>
+      <c r="W93" s="14">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="O94" s="30">
         <v>4</v>
       </c>
-      <c r="H70" s="14">
+      <c r="P94" s="14">
+        <v>1153</v>
+      </c>
+      <c r="Q94" s="14">
+        <v>1154</v>
+      </c>
+      <c r="R94" s="14">
+        <v>1155</v>
+      </c>
+      <c r="S94" s="14">
+        <v>1156</v>
+      </c>
+      <c r="T94" s="14">
+        <v>1157</v>
+      </c>
+      <c r="U94" s="14">
+        <v>1158</v>
+      </c>
+      <c r="V94" s="14">
+        <v>1159</v>
+      </c>
+      <c r="W94" s="14">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="O95" s="31">
         <v>5</v>
       </c>
-      <c r="I70" s="14">
-        <v>6</v>
-      </c>
-      <c r="J70" s="14">
-        <v>7</v>
-      </c>
-      <c r="K70" s="14">
-        <v>8</v>
-      </c>
-      <c r="L70" s="14">
-        <v>9</v>
-      </c>
-      <c r="M70" s="14">
-        <v>10</v>
-      </c>
-      <c r="N70" s="14">
-        <v>11</v>
-      </c>
-      <c r="O70" s="14">
-        <v>12</v>
-      </c>
-      <c r="P70" s="14">
-        <v>13</v>
-      </c>
-      <c r="Q70" s="14">
-        <v>14</v>
-      </c>
-      <c r="R70" s="14">
-        <v>15</v>
-      </c>
-      <c r="S70" s="14">
-        <v>16</v>
-      </c>
-      <c r="X70" s="13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="X71" s="13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="X72" s="13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="X73" s="13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="X74" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="X75" s="13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="X76" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="X77" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="X78" s="13">
-        <v>16</v>
+      <c r="P95" s="14">
+        <v>1177</v>
+      </c>
+      <c r="Q95" s="14">
+        <v>1178</v>
+      </c>
+      <c r="R95" s="14">
+        <v>1179</v>
+      </c>
+      <c r="S95" s="14">
+        <v>1180</v>
+      </c>
+      <c r="T95" s="14">
+        <v>1181</v>
+      </c>
+      <c r="U95" s="14">
+        <v>1182</v>
+      </c>
+      <c r="V95" s="14">
+        <v>1183</v>
+      </c>
+      <c r="W95" s="14">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="97" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O97" s="29">
+        <v>1</v>
+      </c>
+      <c r="P97" s="14">
+        <v>1201</v>
+      </c>
+      <c r="Q97" s="14">
+        <v>1202</v>
+      </c>
+      <c r="R97" s="14">
+        <v>1203</v>
+      </c>
+      <c r="S97" s="14">
+        <v>1204</v>
+      </c>
+      <c r="T97" s="14">
+        <v>1205</v>
+      </c>
+      <c r="U97" s="14">
+        <v>1206</v>
+      </c>
+      <c r="V97" s="14">
+        <v>1207</v>
+      </c>
+      <c r="W97" s="14">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="98" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O98" s="30">
+        <v>2</v>
+      </c>
+      <c r="P98" s="14">
+        <v>1225</v>
+      </c>
+      <c r="Q98" s="14">
+        <v>1226</v>
+      </c>
+      <c r="R98" s="14">
+        <v>1227</v>
+      </c>
+      <c r="S98" s="14">
+        <v>1228</v>
+      </c>
+      <c r="T98" s="14">
+        <v>1229</v>
+      </c>
+      <c r="U98" s="14">
+        <v>1230</v>
+      </c>
+      <c r="V98" s="14">
+        <v>1231</v>
+      </c>
+      <c r="W98" s="14">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="99" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O99" s="30">
+        <v>3</v>
+      </c>
+      <c r="P99" s="14">
+        <v>1249</v>
+      </c>
+      <c r="Q99" s="14">
+        <v>1250</v>
+      </c>
+      <c r="R99" s="14">
+        <v>1251</v>
+      </c>
+      <c r="S99" s="14">
+        <v>1252</v>
+      </c>
+      <c r="T99" s="14">
+        <v>1253</v>
+      </c>
+      <c r="U99" s="14">
+        <v>1254</v>
+      </c>
+      <c r="V99" s="14">
+        <v>1255</v>
+      </c>
+      <c r="W99" s="14">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="100" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O100" s="30">
+        <v>4</v>
+      </c>
+      <c r="P100" s="14">
+        <v>1273</v>
+      </c>
+      <c r="Q100" s="14">
+        <v>1274</v>
+      </c>
+      <c r="R100" s="14">
+        <v>1275</v>
+      </c>
+      <c r="S100" s="14">
+        <v>1276</v>
+      </c>
+      <c r="T100" s="14">
+        <v>1277</v>
+      </c>
+      <c r="U100" s="14">
+        <v>1278</v>
+      </c>
+      <c r="V100" s="14">
+        <v>1279</v>
+      </c>
+      <c r="W100" s="14">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="101" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O101" s="31">
+        <v>5</v>
+      </c>
+      <c r="P101" s="14">
+        <v>1297</v>
+      </c>
+      <c r="Q101" s="14">
+        <v>1298</v>
+      </c>
+      <c r="R101" s="14">
+        <v>1299</v>
+      </c>
+      <c r="S101" s="14">
+        <v>1300</v>
+      </c>
+      <c r="T101" s="14">
+        <v>1301</v>
+      </c>
+      <c r="U101" s="14">
+        <v>1302</v>
+      </c>
+      <c r="V101" s="14">
+        <v>1303</v>
+      </c>
+      <c r="W101" s="14">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="103" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O103" s="29">
+        <v>1</v>
+      </c>
+      <c r="P103" s="14">
+        <v>1321</v>
+      </c>
+      <c r="Q103" s="14">
+        <v>1322</v>
+      </c>
+      <c r="R103" s="14">
+        <v>1323</v>
+      </c>
+      <c r="S103" s="14">
+        <v>1324</v>
+      </c>
+      <c r="T103" s="14">
+        <v>1325</v>
+      </c>
+      <c r="U103" s="14">
+        <v>1326</v>
+      </c>
+      <c r="V103" s="14">
+        <v>1327</v>
+      </c>
+      <c r="W103" s="14">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="104" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O104" s="30">
+        <v>2</v>
+      </c>
+      <c r="P104" s="14">
+        <v>1345</v>
+      </c>
+      <c r="Q104" s="14">
+        <v>1346</v>
+      </c>
+      <c r="R104" s="14">
+        <v>1347</v>
+      </c>
+      <c r="S104" s="14">
+        <v>1348</v>
+      </c>
+      <c r="T104" s="14">
+        <v>1349</v>
+      </c>
+      <c r="U104" s="14">
+        <v>1350</v>
+      </c>
+      <c r="V104" s="14">
+        <v>1351</v>
+      </c>
+      <c r="W104" s="14">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="105" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O105" s="30">
+        <v>3</v>
+      </c>
+      <c r="P105" s="14">
+        <v>1369</v>
+      </c>
+      <c r="Q105" s="14">
+        <v>1370</v>
+      </c>
+      <c r="R105" s="14">
+        <v>1371</v>
+      </c>
+      <c r="S105" s="14">
+        <v>1372</v>
+      </c>
+      <c r="T105" s="14">
+        <v>1373</v>
+      </c>
+      <c r="U105" s="14">
+        <v>1374</v>
+      </c>
+      <c r="V105" s="14">
+        <v>1375</v>
+      </c>
+      <c r="W105" s="14">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="106" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O106" s="30">
+        <v>4</v>
+      </c>
+      <c r="P106" s="14">
+        <v>1393</v>
+      </c>
+      <c r="Q106" s="14">
+        <v>1394</v>
+      </c>
+      <c r="R106" s="14">
+        <v>1395</v>
+      </c>
+      <c r="S106" s="14">
+        <v>1396</v>
+      </c>
+      <c r="T106" s="14">
+        <v>1397</v>
+      </c>
+      <c r="U106" s="14">
+        <v>1398</v>
+      </c>
+      <c r="V106" s="14">
+        <v>1399</v>
+      </c>
+      <c r="W106" s="14">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="107" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O107" s="31">
+        <v>5</v>
+      </c>
+      <c r="P107" s="14">
+        <v>1417</v>
+      </c>
+      <c r="Q107" s="14">
+        <v>1418</v>
+      </c>
+      <c r="R107" s="14">
+        <v>1419</v>
+      </c>
+      <c r="S107" s="14">
+        <v>1420</v>
+      </c>
+      <c r="T107" s="14">
+        <v>1421</v>
+      </c>
+      <c r="U107" s="14">
+        <v>1422</v>
+      </c>
+      <c r="V107" s="14">
+        <v>1423</v>
+      </c>
+      <c r="W107" s="14">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="109" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O109" s="29">
+        <v>1</v>
+      </c>
+      <c r="P109" s="14">
+        <v>1441</v>
+      </c>
+      <c r="Q109" s="14">
+        <v>1442</v>
+      </c>
+      <c r="R109" s="14">
+        <v>1443</v>
+      </c>
+      <c r="S109" s="14">
+        <v>1444</v>
+      </c>
+      <c r="T109" s="14">
+        <v>1445</v>
+      </c>
+      <c r="U109" s="14">
+        <v>1446</v>
+      </c>
+      <c r="V109" s="14">
+        <v>1447</v>
+      </c>
+      <c r="W109" s="14">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="110" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O110" s="30">
+        <v>2</v>
+      </c>
+      <c r="P110" s="14">
+        <v>1465</v>
+      </c>
+      <c r="Q110" s="14">
+        <v>1466</v>
+      </c>
+      <c r="R110" s="14">
+        <v>1467</v>
+      </c>
+      <c r="S110" s="14">
+        <v>1468</v>
+      </c>
+      <c r="T110" s="14">
+        <v>1469</v>
+      </c>
+      <c r="U110" s="14">
+        <v>1470</v>
+      </c>
+      <c r="V110" s="14">
+        <v>1471</v>
+      </c>
+      <c r="W110" s="14">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="111" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O111" s="30">
+        <v>3</v>
+      </c>
+      <c r="P111" s="14">
+        <v>1489</v>
+      </c>
+      <c r="Q111" s="14">
+        <v>1490</v>
+      </c>
+      <c r="R111" s="14">
+        <v>1491</v>
+      </c>
+      <c r="S111" s="14">
+        <v>1492</v>
+      </c>
+      <c r="T111" s="14">
+        <v>1493</v>
+      </c>
+      <c r="U111" s="14">
+        <v>1494</v>
+      </c>
+      <c r="V111" s="14">
+        <v>1495</v>
+      </c>
+      <c r="W111" s="14">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="112" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O112" s="30">
+        <v>4</v>
+      </c>
+      <c r="P112" s="14">
+        <v>1513</v>
+      </c>
+      <c r="Q112" s="14">
+        <v>1514</v>
+      </c>
+      <c r="R112" s="14">
+        <v>1515</v>
+      </c>
+      <c r="S112" s="14">
+        <v>1516</v>
+      </c>
+      <c r="T112" s="14">
+        <v>1517</v>
+      </c>
+      <c r="U112" s="14">
+        <v>1518</v>
+      </c>
+      <c r="V112" s="14">
+        <v>1519</v>
+      </c>
+      <c r="W112" s="14">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="113" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O113" s="31">
+        <v>5</v>
+      </c>
+      <c r="P113" s="14">
+        <v>1537</v>
+      </c>
+      <c r="Q113" s="14">
+        <v>1538</v>
+      </c>
+      <c r="R113" s="14">
+        <v>1539</v>
+      </c>
+      <c r="S113" s="14">
+        <v>1540</v>
+      </c>
+      <c r="T113" s="14">
+        <v>1541</v>
+      </c>
+      <c r="U113" s="14">
+        <v>1542</v>
+      </c>
+      <c r="V113" s="14">
+        <v>1543</v>
+      </c>
+      <c r="W113" s="14">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="115" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O115" s="29">
+        <v>1</v>
+      </c>
+      <c r="P115" s="14">
+        <v>1561</v>
+      </c>
+      <c r="Q115" s="14">
+        <v>1562</v>
+      </c>
+      <c r="R115" s="14">
+        <v>1563</v>
+      </c>
+      <c r="S115" s="14">
+        <v>1564</v>
+      </c>
+      <c r="T115" s="14">
+        <v>1565</v>
+      </c>
+      <c r="U115" s="14">
+        <v>1566</v>
+      </c>
+      <c r="V115" s="14">
+        <v>1567</v>
+      </c>
+      <c r="W115" s="14">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="116" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O116" s="30">
+        <v>2</v>
+      </c>
+      <c r="P116" s="14">
+        <v>1585</v>
+      </c>
+      <c r="Q116" s="14">
+        <v>1586</v>
+      </c>
+      <c r="R116" s="14">
+        <v>1587</v>
+      </c>
+      <c r="S116" s="14">
+        <v>1588</v>
+      </c>
+      <c r="T116" s="14">
+        <v>1589</v>
+      </c>
+      <c r="U116" s="14">
+        <v>1590</v>
+      </c>
+      <c r="V116" s="14">
+        <v>1591</v>
+      </c>
+      <c r="W116" s="14">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="117" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O117" s="30">
+        <v>3</v>
+      </c>
+      <c r="P117" s="14">
+        <v>1609</v>
+      </c>
+      <c r="Q117" s="14">
+        <v>1610</v>
+      </c>
+      <c r="R117" s="14">
+        <v>1611</v>
+      </c>
+      <c r="S117" s="14">
+        <v>1612</v>
+      </c>
+      <c r="T117" s="14">
+        <v>1613</v>
+      </c>
+      <c r="U117" s="14">
+        <v>1614</v>
+      </c>
+      <c r="V117" s="14">
+        <v>1615</v>
+      </c>
+      <c r="W117" s="14">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="118" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O118" s="30">
+        <v>4</v>
+      </c>
+      <c r="P118" s="14">
+        <v>1633</v>
+      </c>
+      <c r="Q118" s="14">
+        <v>1634</v>
+      </c>
+      <c r="R118" s="14">
+        <v>1635</v>
+      </c>
+      <c r="S118" s="14">
+        <v>1636</v>
+      </c>
+      <c r="T118" s="14">
+        <v>1637</v>
+      </c>
+      <c r="U118" s="14">
+        <v>1638</v>
+      </c>
+      <c r="V118" s="14">
+        <v>1639</v>
+      </c>
+      <c r="W118" s="14">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="119" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O119" s="31">
+        <v>5</v>
+      </c>
+      <c r="P119" s="14">
+        <v>1657</v>
+      </c>
+      <c r="Q119" s="14">
+        <v>1658</v>
+      </c>
+      <c r="R119" s="14">
+        <v>1659</v>
+      </c>
+      <c r="S119" s="14">
+        <v>1660</v>
+      </c>
+      <c r="T119" s="14">
+        <v>1661</v>
+      </c>
+      <c r="U119" s="14">
+        <v>1662</v>
+      </c>
+      <c r="V119" s="14">
+        <v>1663</v>
+      </c>
+      <c r="W119" s="14">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="121" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O121" s="29">
+        <v>1</v>
+      </c>
+      <c r="P121" s="14">
+        <v>1681</v>
+      </c>
+      <c r="Q121" s="14">
+        <v>1682</v>
+      </c>
+      <c r="R121" s="14">
+        <v>1683</v>
+      </c>
+      <c r="S121" s="14">
+        <v>1684</v>
+      </c>
+      <c r="T121" s="14">
+        <v>1685</v>
+      </c>
+      <c r="U121" s="14">
+        <v>1686</v>
+      </c>
+      <c r="V121" s="14">
+        <v>1687</v>
+      </c>
+      <c r="W121" s="14">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="122" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O122" s="30">
+        <v>2</v>
+      </c>
+      <c r="P122" s="14">
+        <v>1705</v>
+      </c>
+      <c r="Q122" s="14">
+        <v>1706</v>
+      </c>
+      <c r="R122" s="14">
+        <v>1707</v>
+      </c>
+      <c r="S122" s="14">
+        <v>1708</v>
+      </c>
+      <c r="T122" s="14">
+        <v>1709</v>
+      </c>
+      <c r="U122" s="14">
+        <v>1710</v>
+      </c>
+      <c r="V122" s="14">
+        <v>1711</v>
+      </c>
+      <c r="W122" s="14">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="123" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O123" s="30">
+        <v>3</v>
+      </c>
+      <c r="P123" s="14">
+        <v>1729</v>
+      </c>
+      <c r="Q123" s="14">
+        <v>1730</v>
+      </c>
+      <c r="R123" s="14">
+        <v>1731</v>
+      </c>
+      <c r="S123" s="14">
+        <v>1732</v>
+      </c>
+      <c r="T123" s="14">
+        <v>1733</v>
+      </c>
+      <c r="U123" s="14">
+        <v>1734</v>
+      </c>
+      <c r="V123" s="14">
+        <v>1735</v>
+      </c>
+      <c r="W123" s="14">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="124" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O124" s="30">
+        <v>4</v>
+      </c>
+      <c r="P124" s="14">
+        <v>1753</v>
+      </c>
+      <c r="Q124" s="14">
+        <v>1754</v>
+      </c>
+      <c r="R124" s="14">
+        <v>1755</v>
+      </c>
+      <c r="S124" s="14">
+        <v>1756</v>
+      </c>
+      <c r="T124" s="14">
+        <v>1757</v>
+      </c>
+      <c r="U124" s="14">
+        <v>1758</v>
+      </c>
+      <c r="V124" s="14">
+        <v>1759</v>
+      </c>
+      <c r="W124" s="14">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="125" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O125" s="31">
+        <v>5</v>
+      </c>
+      <c r="P125" s="14">
+        <v>1777</v>
+      </c>
+      <c r="Q125" s="14">
+        <v>1778</v>
+      </c>
+      <c r="R125" s="14">
+        <v>1779</v>
+      </c>
+      <c r="S125" s="14">
+        <v>1780</v>
+      </c>
+      <c r="T125" s="14">
+        <v>1781</v>
+      </c>
+      <c r="U125" s="14">
+        <v>1782</v>
+      </c>
+      <c r="V125" s="14">
+        <v>1783</v>
+      </c>
+      <c r="W125" s="14">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="127" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O127" s="29">
+        <v>1</v>
+      </c>
+      <c r="P127" s="14">
+        <v>1801</v>
+      </c>
+      <c r="Q127" s="14">
+        <v>1802</v>
+      </c>
+      <c r="R127" s="14">
+        <v>1803</v>
+      </c>
+      <c r="S127" s="14">
+        <v>1804</v>
+      </c>
+      <c r="T127" s="14">
+        <v>1805</v>
+      </c>
+      <c r="U127" s="14">
+        <v>1806</v>
+      </c>
+      <c r="V127" s="14">
+        <v>1807</v>
+      </c>
+      <c r="W127" s="14">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="128" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O128" s="30">
+        <v>2</v>
+      </c>
+      <c r="P128" s="14">
+        <v>1825</v>
+      </c>
+      <c r="Q128" s="14">
+        <v>1826</v>
+      </c>
+      <c r="R128" s="14">
+        <v>1827</v>
+      </c>
+      <c r="S128" s="14">
+        <v>1828</v>
+      </c>
+      <c r="T128" s="14">
+        <v>1829</v>
+      </c>
+      <c r="U128" s="14">
+        <v>1830</v>
+      </c>
+      <c r="V128" s="14">
+        <v>1831</v>
+      </c>
+      <c r="W128" s="14">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="129" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O129" s="30">
+        <v>3</v>
+      </c>
+      <c r="P129" s="14">
+        <v>1849</v>
+      </c>
+      <c r="Q129" s="14">
+        <v>1850</v>
+      </c>
+      <c r="R129" s="14">
+        <v>1851</v>
+      </c>
+      <c r="S129" s="14">
+        <v>1852</v>
+      </c>
+      <c r="T129" s="14">
+        <v>1853</v>
+      </c>
+      <c r="U129" s="14">
+        <v>1854</v>
+      </c>
+      <c r="V129" s="14">
+        <v>1855</v>
+      </c>
+      <c r="W129" s="14">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="130" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O130" s="30">
+        <v>4</v>
+      </c>
+      <c r="P130" s="14">
+        <v>1873</v>
+      </c>
+      <c r="Q130" s="14">
+        <v>1874</v>
+      </c>
+      <c r="R130" s="14">
+        <v>1875</v>
+      </c>
+      <c r="S130" s="14">
+        <v>1876</v>
+      </c>
+      <c r="T130" s="14">
+        <v>1877</v>
+      </c>
+      <c r="U130" s="14">
+        <v>1878</v>
+      </c>
+      <c r="V130" s="14">
+        <v>1879</v>
+      </c>
+      <c r="W130" s="14">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="131" spans="15:23" x14ac:dyDescent="0.25">
+      <c r="O131" s="31">
+        <v>5</v>
+      </c>
+      <c r="P131" s="14">
+        <v>1897</v>
+      </c>
+      <c r="Q131" s="14">
+        <v>1898</v>
+      </c>
+      <c r="R131" s="14">
+        <v>1899</v>
+      </c>
+      <c r="S131" s="14">
+        <v>1900</v>
+      </c>
+      <c r="T131" s="14">
+        <v>1901</v>
+      </c>
+      <c r="U131" s="14">
+        <v>1902</v>
+      </c>
+      <c r="V131" s="14">
+        <v>1903</v>
+      </c>
+      <c r="W131" s="14">
+        <v>1904</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="160">
+    <mergeCell ref="AM60:AN60"/>
+    <mergeCell ref="AO60:AP60"/>
+    <mergeCell ref="AQ60:AR60"/>
+    <mergeCell ref="AC33:AD33"/>
+    <mergeCell ref="AE33:AF33"/>
+    <mergeCell ref="AG33:AH33"/>
+    <mergeCell ref="AI33:AJ33"/>
+    <mergeCell ref="AK33:AL33"/>
+    <mergeCell ref="AM33:AN33"/>
+    <mergeCell ref="AO33:AP33"/>
+    <mergeCell ref="AQ33:AR33"/>
+    <mergeCell ref="AC60:AD60"/>
+    <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="AG60:AH60"/>
+    <mergeCell ref="AI60:AJ60"/>
+    <mergeCell ref="AK60:AL60"/>
+    <mergeCell ref="AM58:AN58"/>
+    <mergeCell ref="AO58:AP58"/>
+    <mergeCell ref="AQ58:AR58"/>
+    <mergeCell ref="AC59:AD59"/>
+    <mergeCell ref="AE59:AF59"/>
+    <mergeCell ref="AG59:AH59"/>
+    <mergeCell ref="AI59:AJ59"/>
+    <mergeCell ref="AK59:AL59"/>
+    <mergeCell ref="AM59:AN59"/>
+    <mergeCell ref="AO59:AP59"/>
+    <mergeCell ref="AQ59:AR59"/>
+    <mergeCell ref="AC58:AD58"/>
+    <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="AG58:AH58"/>
+    <mergeCell ref="AI58:AJ58"/>
+    <mergeCell ref="AK58:AL58"/>
+    <mergeCell ref="AM56:AN56"/>
+    <mergeCell ref="AO56:AP56"/>
+    <mergeCell ref="AQ56:AR56"/>
+    <mergeCell ref="AC57:AD57"/>
+    <mergeCell ref="AE57:AF57"/>
+    <mergeCell ref="AG57:AH57"/>
+    <mergeCell ref="AI57:AJ57"/>
+    <mergeCell ref="AK57:AL57"/>
+    <mergeCell ref="AM57:AN57"/>
+    <mergeCell ref="AO57:AP57"/>
+    <mergeCell ref="AQ57:AR57"/>
+    <mergeCell ref="AC56:AD56"/>
+    <mergeCell ref="AE56:AF56"/>
+    <mergeCell ref="AG56:AH56"/>
+    <mergeCell ref="AI56:AJ56"/>
+    <mergeCell ref="AK56:AL56"/>
+    <mergeCell ref="AM54:AN54"/>
+    <mergeCell ref="AO54:AP54"/>
+    <mergeCell ref="AQ54:AR54"/>
+    <mergeCell ref="AC55:AD55"/>
+    <mergeCell ref="AE55:AF55"/>
+    <mergeCell ref="AG55:AH55"/>
+    <mergeCell ref="AI55:AJ55"/>
+    <mergeCell ref="AK55:AL55"/>
+    <mergeCell ref="AM55:AN55"/>
+    <mergeCell ref="AO55:AP55"/>
+    <mergeCell ref="AQ55:AR55"/>
+    <mergeCell ref="AC54:AD54"/>
+    <mergeCell ref="AE54:AF54"/>
+    <mergeCell ref="AG54:AH54"/>
+    <mergeCell ref="AI54:AJ54"/>
+    <mergeCell ref="AK54:AL54"/>
+    <mergeCell ref="AM52:AN52"/>
+    <mergeCell ref="AO52:AP52"/>
+    <mergeCell ref="AQ52:AR52"/>
+    <mergeCell ref="AC53:AD53"/>
+    <mergeCell ref="AE53:AF53"/>
+    <mergeCell ref="AG53:AH53"/>
+    <mergeCell ref="AI53:AJ53"/>
+    <mergeCell ref="AK53:AL53"/>
+    <mergeCell ref="AM53:AN53"/>
+    <mergeCell ref="AO53:AP53"/>
+    <mergeCell ref="AQ53:AR53"/>
+    <mergeCell ref="AC52:AD52"/>
+    <mergeCell ref="AE52:AF52"/>
+    <mergeCell ref="AG52:AH52"/>
+    <mergeCell ref="AI52:AJ52"/>
+    <mergeCell ref="AK52:AL52"/>
+    <mergeCell ref="AM50:AN50"/>
+    <mergeCell ref="AO50:AP50"/>
+    <mergeCell ref="AQ50:AR50"/>
+    <mergeCell ref="AC51:AD51"/>
+    <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AG51:AH51"/>
+    <mergeCell ref="AI51:AJ51"/>
+    <mergeCell ref="AK51:AL51"/>
+    <mergeCell ref="AM51:AN51"/>
+    <mergeCell ref="AO51:AP51"/>
+    <mergeCell ref="AQ51:AR51"/>
+    <mergeCell ref="AC50:AD50"/>
+    <mergeCell ref="AE50:AF50"/>
+    <mergeCell ref="AG50:AH50"/>
+    <mergeCell ref="AI50:AJ50"/>
+    <mergeCell ref="AK50:AL50"/>
+    <mergeCell ref="AM48:AN48"/>
+    <mergeCell ref="AO48:AP48"/>
+    <mergeCell ref="AQ48:AR48"/>
+    <mergeCell ref="AC49:AD49"/>
+    <mergeCell ref="AE49:AF49"/>
+    <mergeCell ref="AG49:AH49"/>
+    <mergeCell ref="AI49:AJ49"/>
+    <mergeCell ref="AK49:AL49"/>
+    <mergeCell ref="AM49:AN49"/>
+    <mergeCell ref="AO49:AP49"/>
+    <mergeCell ref="AQ49:AR49"/>
+    <mergeCell ref="AC48:AD48"/>
+    <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AG48:AH48"/>
+    <mergeCell ref="AI48:AJ48"/>
+    <mergeCell ref="AK48:AL48"/>
+    <mergeCell ref="AM46:AN46"/>
+    <mergeCell ref="AO46:AP46"/>
+    <mergeCell ref="AQ46:AR46"/>
+    <mergeCell ref="AC47:AD47"/>
+    <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="AG47:AH47"/>
+    <mergeCell ref="AI47:AJ47"/>
+    <mergeCell ref="AK47:AL47"/>
+    <mergeCell ref="AM47:AN47"/>
+    <mergeCell ref="AO47:AP47"/>
+    <mergeCell ref="AQ47:AR47"/>
+    <mergeCell ref="AC46:AD46"/>
+    <mergeCell ref="AE46:AF46"/>
+    <mergeCell ref="AG46:AH46"/>
+    <mergeCell ref="AI46:AJ46"/>
+    <mergeCell ref="AK46:AL46"/>
+    <mergeCell ref="AM43:AN43"/>
+    <mergeCell ref="AO43:AP43"/>
+    <mergeCell ref="AQ43:AR43"/>
+    <mergeCell ref="AC45:AD45"/>
+    <mergeCell ref="AE45:AF45"/>
+    <mergeCell ref="AG45:AH45"/>
+    <mergeCell ref="AI45:AJ45"/>
+    <mergeCell ref="AK45:AL45"/>
+    <mergeCell ref="AM45:AN45"/>
+    <mergeCell ref="AO45:AP45"/>
+    <mergeCell ref="AQ45:AR45"/>
+    <mergeCell ref="AC43:AD43"/>
+    <mergeCell ref="AE43:AF43"/>
+    <mergeCell ref="AG43:AH43"/>
+    <mergeCell ref="AI43:AJ43"/>
+    <mergeCell ref="AK43:AL43"/>
     <mergeCell ref="AM37:AN37"/>
     <mergeCell ref="AO37:AP37"/>
     <mergeCell ref="AQ37:AR37"/>
